--- a/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_36.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_36.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2978810.917752051</v>
+        <v>2978869.669255396</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7077002.020534816</v>
+        <v>7077002.020534817</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7077002.020534816</v>
+        <v>7077002.020534817</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51065065.24136957</v>
+        <v>51065065.24136955</v>
       </c>
     </row>
   </sheetData>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>21.64176186434823</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>2.684005452845383</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>128.0695658391427</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>154</v>
@@ -723,7 +723,7 @@
         <v>154</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -778,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>99.77013301500787</v>
+        <v>55.21077645495438</v>
       </c>
       <c r="R3" t="n">
-        <v>119.9110151020648</v>
+        <v>111.6167029527567</v>
       </c>
       <c r="S3" t="n">
+        <v>55.89659430423393</v>
+      </c>
+      <c r="T3" t="n">
         <v>154</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.042925594872315</v>
       </c>
       <c r="U3" t="n">
         <v>0.172576741318835</v>
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>45.15815238615647</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>97.50620641922586</v>
@@ -854,10 +854,10 @@
         <v>154</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>38.13699358077408</v>
       </c>
       <c r="Q4" t="n">
-        <v>146.9788411946176</v>
+        <v>154</v>
       </c>
       <c r="R4" t="n">
         <v>154</v>
@@ -894,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>135.8320388073026</v>
+        <v>169.0000000000008</v>
       </c>
       <c r="V5" t="n">
         <v>169.0000000000008</v>
@@ -957,7 +957,7 @@
         <v>169.0000000000008</v>
       </c>
       <c r="X5" t="n">
-        <v>169.0000000000008</v>
+        <v>96.6966163041584</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>80.37985086008206</v>
       </c>
       <c r="E6" t="n">
-        <v>149.6097178450741</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>99.77013301500787</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>111.6167029527567</v>
@@ -1091,13 +1091,13 @@
         <v>169</v>
       </c>
       <c r="P7" t="n">
-        <v>6.190841194617598</v>
+        <v>169</v>
       </c>
       <c r="Q7" t="n">
         <v>169</v>
       </c>
       <c r="R7" t="n">
-        <v>169</v>
+        <v>6.190841194617581</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,22 +1128,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.684005452845383</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1182,19 +1182,19 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="U8" t="n">
-        <v>170</v>
+        <v>147.0519945471545</v>
       </c>
       <c r="V8" t="n">
         <v>170</v>
       </c>
       <c r="W8" t="n">
-        <v>53.03424169770702</v>
+        <v>170</v>
       </c>
       <c r="X8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>99.77013301500787</v>
       </c>
       <c r="R9" t="n">
         <v>170</v>
       </c>
       <c r="S9" t="n">
-        <v>170</v>
+        <v>55.89659430423393</v>
       </c>
       <c r="T9" t="n">
-        <v>82.81687371194495</v>
+        <v>3.042925594872315</v>
       </c>
       <c r="U9" t="n">
         <v>0.172576741318835</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>113.9699602432184</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1368,10 +1368,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>137.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>131.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>129.6840054528454</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1419,22 +1419,22 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>19.60797129198799</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>96.58481009929297</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>111.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88.09991244551929</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>69.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>52.16523398823489</v>
       </c>
       <c r="H12" t="n">
-        <v>52.29514752992744</v>
+        <v>53.62154001660981</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>130.0429255948723</v>
       </c>
       <c r="U12" t="n">
-        <v>127.1725767413188</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>141.5106671915202</v>
@@ -1513,7 +1513,7 @@
         <v>146.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>73.62239654146258</v>
       </c>
     </row>
     <row r="13">
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>78.9653658626972</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>172.0000000000109</v>
+        <v>151.4976000000196</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="O13" t="n">
-        <v>163.5495577131445</v>
+        <v>172</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="Q13" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>80.98267642416691</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,19 +1608,19 @@
         <v>98.47457824299391</v>
       </c>
       <c r="D14" t="n">
-        <v>59.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>53.88962870801186</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>46.01704061307515</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,25 +1653,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>119.3888210686546</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
+        <v>17.41009868445799</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
         <v>172</v>
       </c>
-      <c r="V14" t="n">
-        <v>165.6838660171562</v>
-      </c>
-      <c r="W14" t="n">
-        <v>172</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>160.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>155.5910919548585</v>
+        <v>160.6167029527567</v>
       </c>
       <c r="S15" t="n">
-        <v>104.8965943042339</v>
+        <v>99.87098330633573</v>
       </c>
       <c r="T15" t="n">
         <v>52.04292559487232</v>
@@ -1793,22 +1793,22 @@
         <v>0.9653658626971833</v>
       </c>
       <c r="M16" t="n">
-        <v>94.15815238615647</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>146.5062064192259</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>172</v>
       </c>
       <c r="P16" t="n">
-        <v>78.88519890775349</v>
+        <v>172</v>
       </c>
       <c r="Q16" t="n">
+        <v>147.5495577131358</v>
+      </c>
+      <c r="R16" t="n">
         <v>172</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>2.982676424166925</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>46.01704061307515</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>119.3888210686546</v>
+        <v>105.4805593869247</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -1899,16 +1899,16 @@
         <v>172</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="W17" t="n">
         <v>172</v>
       </c>
       <c r="X17" t="n">
-        <v>43.79134624853901</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>160.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9653658626971975</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>94.15815238615646</v>
       </c>
       <c r="N19" t="n">
         <v>146.5062064192259</v>
@@ -2039,16 +2039,16 @@
         <v>172</v>
       </c>
       <c r="P19" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.043351293909974</v>
+        <v>82.8332411946176</v>
       </c>
       <c r="R19" t="n">
         <v>172</v>
       </c>
       <c r="S19" t="n">
-        <v>2.982676424166913</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>34.5534813573999</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>59.33915573984979</v>
       </c>
       <c r="E20" t="n">
         <v>53.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>53.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>51.68400545284538</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>46.01704061307515</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>119.3888210686546</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="U20" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>29.24761455054424</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2145,7 +2145,7 @@
         <v>188</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>160.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>57.06718900210178</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>57.06718900210178</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>0.9653658626971833</v>
       </c>
       <c r="M22" t="n">
-        <v>94.15815238615647</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>146.5062064192259</v>
@@ -2276,16 +2276,16 @@
         <v>188</v>
       </c>
       <c r="P22" t="n">
+        <v>15.13615129390996</v>
+      </c>
+      <c r="Q22" t="n">
         <v>188</v>
       </c>
-      <c r="Q22" t="n">
-        <v>111.9606753319204</v>
-      </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.982676424166925</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>130.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>98.47457824299391</v>
@@ -2322,13 +2322,13 @@
         <v>59.33915573984979</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>53.36328960686865</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>53.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>51.68400545284538</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2364,22 +2364,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>107.7089413042498</v>
+        <v>119.3888210686546</v>
       </c>
       <c r="T23" t="n">
         <v>230.9769184119809</v>
       </c>
       <c r="U23" t="n">
-        <v>298.135427201877</v>
+        <v>220.9487459191644</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>278.8510241668239</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>241.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>160.3174326828064</v>
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>342</v>
+        <v>33.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>10.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>312.710389002102</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>213.2750413673193</v>
+        <v>160.6167029527567</v>
       </c>
       <c r="S24" t="n">
         <v>104.8965943042339</v>
@@ -2461,7 +2461,7 @@
         <v>68.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>342</v>
+        <v>48.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="C26" t="n">
         <v>173.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>134.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>128.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>118.209152435919</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>121.0170406130752</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2613,10 +2613,10 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>104.8870373091444</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>108.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>85.09991244551929</v>
@@ -2641,7 +2641,7 @@
         <v>66.67209722191262</v>
       </c>
       <c r="F27" t="n">
-        <v>11.24951008956548</v>
+        <v>63.63624233787687</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -2683,10 +2683,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>127.0429255948723</v>
       </c>
       <c r="U27" t="n">
-        <v>124.1725767413188</v>
+        <v>32.82812886520855</v>
       </c>
       <c r="V27" t="n">
         <v>138.5106671915202</v>
@@ -2695,10 +2695,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>143.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>123.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>107.4506128613796</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>29.46793643721265</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>77.98267642416691</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2790,22 +2790,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>97.47457824299391</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>58.33915573984979</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>52.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>50.68400545284535</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>45.01704061307515</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2841,19 +2841,19 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>152.3783999999998</v>
+        <v>20.97399124322384</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="V29" t="n">
         <v>173</v>
       </c>
       <c r="W29" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>8.85518900210174</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2984,16 +2984,16 @@
         <v>145.5062064192259</v>
       </c>
       <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>84.73136477045072</v>
+      </c>
+      <c r="Q31" t="n">
         <v>173</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>173</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>84.73136477045071</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1.982676424166913</v>
@@ -3024,13 +3024,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>46.47457824299391</v>
       </c>
       <c r="D32" t="n">
-        <v>7.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>1.363289606868648</v>
@@ -3078,19 +3078,19 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>165.4526707593191</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>172</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
-        <v>79.11420206389481</v>
+        <v>172</v>
       </c>
       <c r="X32" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>108.3174326828064</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,28 +3148,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>99.77013301500787</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>113.084323134022</v>
+        <v>108.6167029527567</v>
       </c>
       <c r="S33" t="n">
         <v>52.89659430423393</v>
       </c>
       <c r="T33" t="n">
+        <v>0.04292559486835623</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
         <v>172</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>11.51066719152016</v>
-      </c>
       <c r="W33" t="n">
-        <v>29.37314290982852</v>
+        <v>172</v>
       </c>
       <c r="X33" t="n">
-        <v>16.86273944538755</v>
+        <v>161.9413771481409</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3264,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>46.47457824299391</v>
       </c>
       <c r="D35" t="n">
-        <v>7.339155739849787</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>1.363289606868648</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>139.1439259452696</v>
+        <v>100.0085034421256</v>
       </c>
       <c r="U35" t="n">
         <v>170</v>
@@ -3324,10 +3324,10 @@
         <v>170</v>
       </c>
       <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
         <v>170</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3346,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>111.9438947929242</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3391,16 +3391,16 @@
         <v>108.6167029527567</v>
       </c>
       <c r="S36" t="n">
-        <v>52.89659430423393</v>
+        <v>170</v>
       </c>
       <c r="T36" t="n">
-        <v>0.0429255948690952</v>
+        <v>0.04292559486864045</v>
       </c>
       <c r="U36" t="n">
-        <v>170</v>
+        <v>153.3298219056385</v>
       </c>
       <c r="V36" t="n">
-        <v>170</v>
+        <v>11.51066719152016</v>
       </c>
       <c r="W36" t="n">
         <v>29.37314290982852</v>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>42.15815238615647</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>94.50620641922586</v>
@@ -3461,10 +3461,10 @@
         <v>169.3912034232773</v>
       </c>
       <c r="P37" t="n">
-        <v>13.68043777134042</v>
+        <v>170</v>
       </c>
       <c r="Q37" t="n">
-        <v>170</v>
+        <v>55.83859015749687</v>
       </c>
       <c r="R37" t="n">
         <v>170</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>78.99931295557451</v>
       </c>
       <c r="C38" t="n">
         <v>46.47457824299391</v>
@@ -3549,22 +3549,22 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>67.38882106865458</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="U38" t="n">
-        <v>154.3519150194694</v>
+        <v>170</v>
       </c>
       <c r="V38" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>7.963780995240276</v>
       </c>
       <c r="Y38" t="n">
         <v>108.3174326828064</v>
@@ -3598,7 +3598,7 @@
         <v>170</v>
       </c>
       <c r="I39" t="n">
-        <v>100.4332276014039</v>
+        <v>100.4761531962731</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>52.89659430423393</v>
       </c>
       <c r="T39" t="n">
-        <v>0.04292559486920888</v>
+        <v>170</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>16.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3689,19 +3689,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>42.15815238615647</v>
       </c>
       <c r="N40" t="n">
         <v>94.50620641922586</v>
       </c>
       <c r="O40" t="n">
-        <v>169.3912034232773</v>
+        <v>13.0716411946177</v>
       </c>
       <c r="P40" t="n">
         <v>170</v>
       </c>
       <c r="Q40" t="n">
-        <v>55.83859015749687</v>
+        <v>170</v>
       </c>
       <c r="R40" t="n">
         <v>170</v>
@@ -3735,61 +3735,61 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>170</v>
       </c>
-      <c r="C41" t="n">
+      <c r="G41" t="n">
         <v>170</v>
       </c>
-      <c r="D41" t="n">
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
         <v>170</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>149.736</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>149.736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3817,22 +3817,22 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>155.0999124455193</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>136.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>77.34245031595825</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>120.6215400166098</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,22 +3862,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
         <v>170</v>
       </c>
-      <c r="S42" t="n">
-        <v>149.736</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
       <c r="V42" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>18.49037200325796</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3920,16 +3920,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>26.5820852765529</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>77.91592730353183</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>147.9826764241669</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>1.967353391503622</v>
@@ -3959,10 +3959,10 @@
         <v>20.37280983870968</v>
       </c>
       <c r="X43" t="n">
-        <v>41.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>13.41714816944651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3975,13 +3975,13 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
         <v>154</v>
       </c>
-      <c r="D44" t="n">
-        <v>78.94301519168725</v>
-      </c>
       <c r="E44" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4020,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>131.4537194313095</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
         <v>154</v>
       </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>101.4892957603777</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4054,55 +4054,55 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>87.87306698499216</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>47.77013301500788</v>
+      </c>
+      <c r="R45" t="n">
         <v>154</v>
       </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>144.2899273161986</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>145.3532726838014</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -4114,10 +4114,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="X45" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4187,10 +4187,10 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
         <v>49.76101252297596</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.97013551601741</v>
+        <v>15.03111661903574</v>
       </c>
       <c r="C2" t="n">
-        <v>19.97013551601741</v>
+        <v>15.03111661903574</v>
       </c>
       <c r="D2" t="n">
-        <v>19.97013551601741</v>
+        <v>15.03111661903574</v>
       </c>
       <c r="E2" t="n">
-        <v>19.97013551601741</v>
+        <v>15.03111661903574</v>
       </c>
       <c r="F2" t="n">
         <v>15.03111661903574</v>
@@ -4354,19 +4354,19 @@
         <v>616</v>
       </c>
       <c r="U2" t="n">
-        <v>486.6368021826842</v>
+        <v>616</v>
       </c>
       <c r="V2" t="n">
-        <v>331.0812466271286</v>
+        <v>460.4444444444445</v>
       </c>
       <c r="W2" t="n">
-        <v>175.525691071573</v>
+        <v>304.8888888888889</v>
       </c>
       <c r="X2" t="n">
-        <v>19.97013551601741</v>
+        <v>149.3333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.97013551601741</v>
+        <v>36.89148213857941</v>
       </c>
     </row>
     <row r="3">
@@ -4406,28 +4406,28 @@
         <v>164.78</v>
       </c>
       <c r="L3" t="n">
-        <v>317.24</v>
+        <v>175.3716095377359</v>
       </c>
       <c r="M3" t="n">
-        <v>459.4000532715052</v>
+        <v>311.0799999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>611.8600532715052</v>
+        <v>463.54</v>
       </c>
       <c r="O3" t="n">
-        <v>611.8600532715052</v>
+        <v>463.54</v>
       </c>
       <c r="P3" t="n">
         <v>616</v>
       </c>
       <c r="Q3" t="n">
-        <v>515.2220878636284</v>
+        <v>560.2315389343895</v>
       </c>
       <c r="R3" t="n">
-        <v>394.0998503867953</v>
+        <v>447.4873945376656</v>
       </c>
       <c r="S3" t="n">
-        <v>238.5442948312398</v>
+        <v>391.0261881697526</v>
       </c>
       <c r="T3" t="n">
         <v>235.470632614197</v>
@@ -4455,22 +4455,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>474.206451019107</v>
+        <v>463.54</v>
       </c>
       <c r="C4" t="n">
-        <v>600.2084568375427</v>
+        <v>463.54</v>
       </c>
       <c r="D4" t="n">
-        <v>616</v>
+        <v>463.54</v>
       </c>
       <c r="E4" t="n">
-        <v>616</v>
+        <v>463.54</v>
       </c>
       <c r="F4" t="n">
-        <v>616</v>
+        <v>463.54</v>
       </c>
       <c r="G4" t="n">
-        <v>616</v>
+        <v>463.54</v>
       </c>
       <c r="H4" t="n">
         <v>616</v>
@@ -4488,16 +4488,16 @@
         <v>616</v>
       </c>
       <c r="M4" t="n">
-        <v>570.385704660448</v>
+        <v>616</v>
       </c>
       <c r="N4" t="n">
-        <v>471.8945870652704</v>
+        <v>517.5088824048223</v>
       </c>
       <c r="O4" t="n">
-        <v>316.3390315097148</v>
+        <v>361.9533268492668</v>
       </c>
       <c r="P4" t="n">
-        <v>316.3390315097148</v>
+        <v>323.4311111111111</v>
       </c>
       <c r="Q4" t="n">
         <v>167.8755555555556</v>
@@ -4509,22 +4509,22 @@
         <v>57.87715034007474</v>
       </c>
       <c r="T4" t="n">
-        <v>210.3371503400747</v>
+        <v>57.87715034007474</v>
       </c>
       <c r="U4" t="n">
         <v>210.3371503400747</v>
       </c>
       <c r="V4" t="n">
-        <v>362.7971503400747</v>
+        <v>210.3371503400747</v>
       </c>
       <c r="W4" t="n">
-        <v>362.7971503400747</v>
+        <v>210.3371503400747</v>
       </c>
       <c r="X4" t="n">
-        <v>362.7971503400747</v>
+        <v>351.7826623337078</v>
       </c>
       <c r="Y4" t="n">
-        <v>474.206451019107</v>
+        <v>351.7826623337078</v>
       </c>
     </row>
     <row r="5">
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.67470827544967</v>
+        <v>66.20543807660536</v>
       </c>
       <c r="C5" t="n">
-        <v>26.67470827544967</v>
+        <v>16.23111661903574</v>
       </c>
       <c r="D5" t="n">
         <v>16.23111661903574</v>
@@ -4591,19 +4591,19 @@
         <v>676</v>
       </c>
       <c r="U5" t="n">
-        <v>538.7959203966641</v>
+        <v>505.2929292929285</v>
       </c>
       <c r="V5" t="n">
-        <v>368.0888496895926</v>
+        <v>334.5858585858571</v>
       </c>
       <c r="W5" t="n">
-        <v>197.3817789825212</v>
+        <v>163.8787878787856</v>
       </c>
       <c r="X5" t="n">
-        <v>26.67470827544967</v>
+        <v>66.20543807660536</v>
       </c>
       <c r="Y5" t="n">
-        <v>26.67470827544967</v>
+        <v>66.20543807660536</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>335.3479978233073</v>
+        <v>265.4188392526082</v>
       </c>
       <c r="C6" t="n">
-        <v>335.3479978233073</v>
+        <v>94.71176854553744</v>
       </c>
       <c r="D6" t="n">
-        <v>335.3479978233073</v>
+        <v>13.52</v>
       </c>
       <c r="E6" t="n">
-        <v>184.2270707070707</v>
+        <v>13.52</v>
       </c>
       <c r="F6" t="n">
         <v>13.52</v>
@@ -4637,10 +4637,10 @@
         <v>13.52</v>
       </c>
       <c r="J6" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="K6" t="n">
         <v>180.83</v>
-      </c>
-      <c r="K6" t="n">
-        <v>330.7883904622641</v>
       </c>
       <c r="L6" t="n">
         <v>341.38</v>
@@ -4649,7 +4649,7 @@
         <v>341.38</v>
       </c>
       <c r="N6" t="n">
-        <v>341.38</v>
+        <v>508.69</v>
       </c>
       <c r="O6" t="n">
         <v>508.69</v>
@@ -4658,31 +4658,31 @@
         <v>676</v>
       </c>
       <c r="Q6" t="n">
-        <v>575.2220878636284</v>
+        <v>676</v>
       </c>
       <c r="R6" t="n">
-        <v>462.4779434669045</v>
+        <v>563.2558556032761</v>
       </c>
       <c r="S6" t="n">
-        <v>406.0167370989914</v>
+        <v>506.7946492353631</v>
       </c>
       <c r="T6" t="n">
-        <v>402.9430748819487</v>
+        <v>503.7209870183203</v>
       </c>
       <c r="U6" t="n">
-        <v>402.7687549412226</v>
+        <v>503.5466670775942</v>
       </c>
       <c r="V6" t="n">
-        <v>388.1115153538285</v>
+        <v>488.8894274902001</v>
       </c>
       <c r="W6" t="n">
-        <v>355.4113710004664</v>
+        <v>456.189283136838</v>
       </c>
       <c r="X6" t="n">
-        <v>335.3479978233073</v>
+        <v>436.1259099596789</v>
       </c>
       <c r="Y6" t="n">
-        <v>335.3479978233073</v>
+        <v>436.1259099596789</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="C7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="E7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="F7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="G7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="H7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="I7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
       <c r="J7" t="n">
         <v>676</v>
@@ -4734,10 +4734,10 @@
         <v>361.1875163581996</v>
       </c>
       <c r="P7" t="n">
-        <v>354.9341414141414</v>
+        <v>190.4804456511289</v>
       </c>
       <c r="Q7" t="n">
-        <v>184.2270707070707</v>
+        <v>19.77337494405816</v>
       </c>
       <c r="R7" t="n">
         <v>13.52</v>
@@ -4749,19 +4749,19 @@
         <v>13.52</v>
       </c>
       <c r="U7" t="n">
-        <v>78.93990829677421</v>
+        <v>13.52</v>
       </c>
       <c r="V7" t="n">
-        <v>246.2499082967742</v>
+        <v>180.83</v>
       </c>
       <c r="W7" t="n">
-        <v>413.5599082967742</v>
+        <v>348.14</v>
       </c>
       <c r="X7" t="n">
-        <v>564.5906993209677</v>
+        <v>499.1707910241935</v>
       </c>
       <c r="Y7" t="n">
-        <v>676</v>
+        <v>508.69</v>
       </c>
     </row>
     <row r="8">
@@ -4771,19 +4771,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.45095489567519</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="C8" t="n">
-        <v>28.45095489567519</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="D8" t="n">
-        <v>18.00736323926126</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="E8" t="n">
-        <v>13.6</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="F8" t="n">
-        <v>13.6</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="G8" t="n">
         <v>13.6</v>
@@ -4798,22 +4798,22 @@
         <v>69.09708547565204</v>
       </c>
       <c r="K8" t="n">
-        <v>237.397085475652</v>
+        <v>204.2680090434912</v>
       </c>
       <c r="L8" t="n">
-        <v>405.088568792235</v>
+        <v>371.9594923600741</v>
       </c>
       <c r="M8" t="n">
-        <v>417.9798689618422</v>
+        <v>371.9594923600742</v>
       </c>
       <c r="N8" t="n">
-        <v>417.9798689618422</v>
+        <v>371.9594923600742</v>
       </c>
       <c r="O8" t="n">
-        <v>527.4762119025861</v>
+        <v>481.4558353008181</v>
       </c>
       <c r="P8" t="n">
-        <v>680</v>
+        <v>633.979623398232</v>
       </c>
       <c r="Q8" t="n">
         <v>680</v>
@@ -4825,22 +4825,22 @@
         <v>680</v>
       </c>
       <c r="T8" t="n">
-        <v>680</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="U8" t="n">
-        <v>508.2828282828283</v>
+        <v>359.7454600533792</v>
       </c>
       <c r="V8" t="n">
-        <v>336.5656565656566</v>
+        <v>188.0282883362075</v>
       </c>
       <c r="W8" t="n">
-        <v>282.9957154568616</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="X8" t="n">
-        <v>111.2785437396898</v>
+        <v>16.31111661903574</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.2785437396898</v>
+        <v>16.31111661903574</v>
       </c>
     </row>
     <row r="9">
@@ -4874,46 +4874,46 @@
         <v>13.6</v>
       </c>
       <c r="J9" t="n">
-        <v>181.9</v>
+        <v>170.9600532715052</v>
       </c>
       <c r="K9" t="n">
-        <v>181.9</v>
+        <v>170.9600532715052</v>
       </c>
       <c r="L9" t="n">
-        <v>350.2</v>
+        <v>339.2600532715052</v>
       </c>
       <c r="M9" t="n">
-        <v>511.7</v>
+        <v>507.5600532715052</v>
       </c>
       <c r="N9" t="n">
-        <v>511.7</v>
+        <v>675.8600532715052</v>
       </c>
       <c r="O9" t="n">
-        <v>511.7</v>
+        <v>675.8600532715052</v>
       </c>
       <c r="P9" t="n">
         <v>680</v>
       </c>
       <c r="Q9" t="n">
-        <v>680</v>
+        <v>579.2220878636284</v>
       </c>
       <c r="R9" t="n">
-        <v>508.2828282828283</v>
+        <v>407.5049161464567</v>
       </c>
       <c r="S9" t="n">
-        <v>336.5656565656566</v>
+        <v>351.0437097785436</v>
       </c>
       <c r="T9" t="n">
-        <v>252.9122487758132</v>
+        <v>347.9700475615009</v>
       </c>
       <c r="U9" t="n">
-        <v>252.7379288350871</v>
+        <v>347.7957276207748</v>
       </c>
       <c r="V9" t="n">
-        <v>238.080689247693</v>
+        <v>333.1384880333807</v>
       </c>
       <c r="W9" t="n">
-        <v>205.3805448943309</v>
+        <v>300.4383436800186</v>
       </c>
       <c r="X9" t="n">
         <v>185.3171717171717</v>
@@ -4938,25 +4938,25 @@
         <v>13.6</v>
       </c>
       <c r="E10" t="n">
-        <v>131.428904211413</v>
+        <v>13.6</v>
       </c>
       <c r="F10" t="n">
-        <v>255.7898768033485</v>
+        <v>13.6</v>
       </c>
       <c r="G10" t="n">
-        <v>409.6731033459715</v>
+        <v>167.483226542623</v>
       </c>
       <c r="H10" t="n">
-        <v>577.9731033459716</v>
+        <v>335.783226542623</v>
       </c>
       <c r="I10" t="n">
-        <v>680</v>
+        <v>466.7019766278576</v>
       </c>
       <c r="J10" t="n">
-        <v>680</v>
+        <v>466.7019766278576</v>
       </c>
       <c r="K10" t="n">
-        <v>680</v>
+        <v>632.4457122040702</v>
       </c>
       <c r="L10" t="n">
         <v>680</v>
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>146.98184717981</v>
+        <v>590.4395857582899</v>
       </c>
       <c r="C11" t="n">
-        <v>146.98184717981</v>
+        <v>416.7022120209161</v>
       </c>
       <c r="D11" t="n">
-        <v>146.98184717981</v>
+        <v>277.9757920816739</v>
       </c>
       <c r="E11" t="n">
-        <v>146.98184717981</v>
+        <v>277.9757920816739</v>
       </c>
       <c r="F11" t="n">
-        <v>13.76</v>
+        <v>144.753944901864</v>
       </c>
       <c r="G11" t="n">
         <v>13.76</v>
@@ -5035,22 +5035,22 @@
         <v>69.25708547565205</v>
       </c>
       <c r="K11" t="n">
-        <v>204.4280090434912</v>
+        <v>239.537085475652</v>
       </c>
       <c r="L11" t="n">
-        <v>372.1194923600742</v>
+        <v>407.228568792235</v>
       </c>
       <c r="M11" t="n">
-        <v>372.1194923600742</v>
+        <v>407.228568792235</v>
       </c>
       <c r="N11" t="n">
-        <v>372.1194923600742</v>
+        <v>425.9798689618422</v>
       </c>
       <c r="O11" t="n">
-        <v>481.6158353008181</v>
+        <v>535.4762119025861</v>
       </c>
       <c r="P11" t="n">
-        <v>634.1396233982319</v>
+        <v>688</v>
       </c>
       <c r="Q11" t="n">
         <v>688</v>
@@ -5062,22 +5062,22 @@
         <v>688</v>
       </c>
       <c r="T11" t="n">
-        <v>514.2626262626262</v>
+        <v>688</v>
       </c>
       <c r="U11" t="n">
-        <v>494.4565946545575</v>
+        <v>688</v>
       </c>
       <c r="V11" t="n">
-        <v>320.7192209171837</v>
+        <v>688</v>
       </c>
       <c r="W11" t="n">
-        <v>320.7192209171837</v>
+        <v>688</v>
       </c>
       <c r="X11" t="n">
-        <v>146.98184717981</v>
+        <v>688</v>
       </c>
       <c r="Y11" t="n">
-        <v>146.98184717981</v>
+        <v>590.4395857582899</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155.5731918943906</v>
+        <v>190.9911830573307</v>
       </c>
       <c r="C12" t="n">
-        <v>66.58338134336105</v>
+        <v>190.9911830573307</v>
       </c>
       <c r="D12" t="n">
-        <v>66.58338134336105</v>
+        <v>190.9911830573307</v>
       </c>
       <c r="E12" t="n">
-        <v>66.58338134336105</v>
+        <v>120.6153272776209</v>
       </c>
       <c r="F12" t="n">
-        <v>66.58338134336105</v>
+        <v>120.6153272776209</v>
       </c>
       <c r="G12" t="n">
-        <v>66.58338134336105</v>
+        <v>67.92317173394932</v>
       </c>
       <c r="H12" t="n">
         <v>13.76</v>
@@ -5117,16 +5117,16 @@
         <v>13.76</v>
       </c>
       <c r="L12" t="n">
-        <v>184.04</v>
+        <v>177.1600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>354.32</v>
+        <v>347.4400000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>524.6</v>
+        <v>517.72</v>
       </c>
       <c r="O12" t="n">
-        <v>524.6</v>
+        <v>517.72</v>
       </c>
       <c r="P12" t="n">
         <v>688</v>
@@ -5141,22 +5141,22 @@
         <v>688</v>
       </c>
       <c r="T12" t="n">
-        <v>688</v>
+        <v>556.643509500129</v>
       </c>
       <c r="U12" t="n">
-        <v>559.5428517764456</v>
+        <v>556.643509500129</v>
       </c>
       <c r="V12" t="n">
-        <v>416.6027839062232</v>
+        <v>413.7034416299066</v>
       </c>
       <c r="W12" t="n">
-        <v>416.6027839062232</v>
+        <v>413.7034416299066</v>
       </c>
       <c r="X12" t="n">
-        <v>268.2565824462357</v>
+        <v>265.3572401699191</v>
       </c>
       <c r="Y12" t="n">
-        <v>268.2565824462357</v>
+        <v>190.9911830573307</v>
       </c>
     </row>
     <row r="13">
@@ -5196,25 +5196,25 @@
         <v>688.0000000000198</v>
       </c>
       <c r="L13" t="n">
-        <v>608.2370041791135</v>
+        <v>688.0000000000198</v>
       </c>
       <c r="M13" t="n">
-        <v>434.4996304417288</v>
+        <v>534.9721212121212</v>
       </c>
       <c r="N13" t="n">
-        <v>434.4996304417288</v>
+        <v>361.2347474747475</v>
       </c>
       <c r="O13" t="n">
-        <v>269.298056994108</v>
+        <v>187.4973737373737</v>
       </c>
       <c r="P13" t="n">
-        <v>269.298056994108</v>
+        <v>13.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>95.56068325673427</v>
+        <v>13.76</v>
       </c>
       <c r="R13" t="n">
-        <v>95.56068325673427</v>
+        <v>13.76</v>
       </c>
       <c r="S13" t="n">
         <v>13.76</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>173.1678121038825</v>
+        <v>214.1450985495767</v>
       </c>
       <c r="C14" t="n">
-        <v>73.69854115136343</v>
+        <v>114.6758275970576</v>
       </c>
       <c r="D14" t="n">
-        <v>13.76</v>
+        <v>114.6758275970576</v>
       </c>
       <c r="E14" t="n">
-        <v>13.76</v>
+        <v>114.6758275970576</v>
       </c>
       <c r="F14" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="G14" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="H14" t="n">
         <v>13.76</v>
@@ -5272,13 +5272,13 @@
         <v>69.25708547565205</v>
       </c>
       <c r="K14" t="n">
-        <v>239.537085475652</v>
+        <v>204.4280090434912</v>
       </c>
       <c r="L14" t="n">
-        <v>408.2236570592561</v>
+        <v>374.7080090434912</v>
       </c>
       <c r="M14" t="n">
-        <v>408.2236570592561</v>
+        <v>374.7080090434912</v>
       </c>
       <c r="N14" t="n">
         <v>408.2236570592561</v>
@@ -5296,25 +5296,25 @@
         <v>688</v>
       </c>
       <c r="S14" t="n">
-        <v>688</v>
+        <v>567.4052312437832</v>
       </c>
       <c r="T14" t="n">
-        <v>688</v>
+        <v>567.4052312437832</v>
       </c>
       <c r="U14" t="n">
-        <v>514.2626262626262</v>
+        <v>549.8192729766539</v>
       </c>
       <c r="V14" t="n">
-        <v>346.9051858412563</v>
+        <v>549.8192729766539</v>
       </c>
       <c r="W14" t="n">
-        <v>173.1678121038825</v>
+        <v>549.8192729766539</v>
       </c>
       <c r="X14" t="n">
-        <v>173.1678121038825</v>
+        <v>376.0818992392801</v>
       </c>
       <c r="Y14" t="n">
-        <v>173.1678121038825</v>
+        <v>214.1450985495767</v>
       </c>
     </row>
     <row r="15">
@@ -5351,19 +5351,19 @@
         <v>184.04</v>
       </c>
       <c r="K15" t="n">
-        <v>184.04</v>
+        <v>336.8483904622642</v>
       </c>
       <c r="L15" t="n">
-        <v>354.32</v>
+        <v>347.4400000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>524.6</v>
+        <v>517.72</v>
       </c>
       <c r="N15" t="n">
-        <v>683.8600532715052</v>
+        <v>517.72</v>
       </c>
       <c r="O15" t="n">
-        <v>683.8600532715052</v>
+        <v>517.72</v>
       </c>
       <c r="P15" t="n">
         <v>688</v>
@@ -5372,7 +5372,7 @@
         <v>688</v>
       </c>
       <c r="R15" t="n">
-        <v>530.8372808536783</v>
+        <v>525.7609061083266</v>
       </c>
       <c r="S15" t="n">
         <v>424.8811249908157</v>
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>400.5289732532156</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="C16" t="n">
-        <v>478.0209790716514</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="D16" t="n">
-        <v>542.8301231966515</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="E16" t="n">
-        <v>612.1490274080645</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="F16" t="n">
-        <v>688</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="G16" t="n">
-        <v>688</v>
+        <v>275.2417327070127</v>
       </c>
       <c r="H16" t="n">
-        <v>688</v>
+        <v>400.4862644237874</v>
       </c>
       <c r="I16" t="n">
-        <v>688</v>
+        <v>570.7662644237873</v>
       </c>
       <c r="J16" t="n">
-        <v>688</v>
+        <v>570.7662644237873</v>
       </c>
       <c r="K16" t="n">
         <v>688</v>
@@ -5436,19 +5436,19 @@
         <v>687.0248829669725</v>
       </c>
       <c r="M16" t="n">
-        <v>591.915638132471</v>
+        <v>687.0248829669725</v>
       </c>
       <c r="N16" t="n">
-        <v>443.9295710423439</v>
+        <v>687.0248829669725</v>
       </c>
       <c r="O16" t="n">
-        <v>270.1921973049701</v>
+        <v>513.2875092295988</v>
       </c>
       <c r="P16" t="n">
+        <v>339.550135492225</v>
+      </c>
+      <c r="Q16" t="n">
         <v>190.5101782062292</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>16.77280446885548</v>
       </c>
       <c r="R16" t="n">
         <v>16.77280446885548</v>
@@ -5457,22 +5457,22 @@
         <v>13.76</v>
       </c>
       <c r="T16" t="n">
-        <v>155.3623201424114</v>
+        <v>13.76</v>
       </c>
       <c r="U16" t="n">
-        <v>155.3623201424114</v>
+        <v>19.55711327844378</v>
       </c>
       <c r="V16" t="n">
-        <v>171.8615438836977</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="W16" t="n">
-        <v>171.8615438836977</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="X16" t="n">
-        <v>274.3823349078912</v>
+        <v>169.8685061643897</v>
       </c>
       <c r="Y16" t="n">
-        <v>337.2816355869235</v>
+        <v>169.8685061643897</v>
       </c>
     </row>
     <row r="17">
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="C17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="D17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="E17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="F17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="G17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="H17" t="n">
         <v>13.76</v>
@@ -5533,25 +5533,25 @@
         <v>688</v>
       </c>
       <c r="S17" t="n">
-        <v>567.4052312437833</v>
+        <v>581.4539804172477</v>
       </c>
       <c r="T17" t="n">
-        <v>567.4052312437833</v>
+        <v>581.4539804172477</v>
       </c>
       <c r="U17" t="n">
-        <v>393.6678575064095</v>
+        <v>407.716606679874</v>
       </c>
       <c r="V17" t="n">
-        <v>393.6678575064095</v>
+        <v>233.9792329425002</v>
       </c>
       <c r="W17" t="n">
-        <v>219.9304837690358</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="X17" t="n">
-        <v>175.6968006897034</v>
+        <v>60.24185920512642</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.76</v>
+        <v>60.24185920512642</v>
       </c>
     </row>
     <row r="18">
@@ -5588,19 +5588,19 @@
         <v>184.04</v>
       </c>
       <c r="K18" t="n">
-        <v>354.32</v>
+        <v>184.04</v>
       </c>
       <c r="L18" t="n">
-        <v>364.9116095377358</v>
+        <v>194.6316095377359</v>
       </c>
       <c r="M18" t="n">
-        <v>364.9116095377358</v>
+        <v>364.9116095377359</v>
       </c>
       <c r="N18" t="n">
-        <v>517.72</v>
+        <v>535.1916095377359</v>
       </c>
       <c r="O18" t="n">
-        <v>517.72</v>
+        <v>535.1916095377359</v>
       </c>
       <c r="P18" t="n">
         <v>688</v>
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>570.7662644237873</v>
+        <v>200.3882559259695</v>
       </c>
       <c r="C19" t="n">
-        <v>570.7662644237873</v>
+        <v>235.5427117786641</v>
       </c>
       <c r="D19" t="n">
-        <v>570.7662644237873</v>
+        <v>300.3518559036642</v>
       </c>
       <c r="E19" t="n">
-        <v>570.7662644237873</v>
+        <v>369.6707601150772</v>
       </c>
       <c r="F19" t="n">
-        <v>570.7662644237873</v>
+        <v>445.5217327070127</v>
       </c>
       <c r="G19" t="n">
-        <v>570.7662644237873</v>
+        <v>445.5217327070127</v>
       </c>
       <c r="H19" t="n">
         <v>570.7662644237873</v>
@@ -5670,46 +5670,46 @@
         <v>688</v>
       </c>
       <c r="L19" t="n">
-        <v>687.0248829669725</v>
+        <v>688</v>
       </c>
       <c r="M19" t="n">
-        <v>687.0248829669725</v>
+        <v>592.8907551654985</v>
       </c>
       <c r="N19" t="n">
-        <v>539.0388158768454</v>
+        <v>444.9046880753714</v>
       </c>
       <c r="O19" t="n">
-        <v>365.3014421394716</v>
+        <v>271.1673143379976</v>
       </c>
       <c r="P19" t="n">
-        <v>191.5640684020979</v>
+        <v>271.1673143379976</v>
       </c>
       <c r="Q19" t="n">
-        <v>190.5101782062292</v>
+        <v>187.4973737373737</v>
       </c>
       <c r="R19" t="n">
-        <v>16.77280446885547</v>
+        <v>13.76</v>
       </c>
       <c r="S19" t="n">
         <v>13.76</v>
       </c>
       <c r="T19" t="n">
-        <v>126.793953278164</v>
+        <v>13.76</v>
       </c>
       <c r="U19" t="n">
-        <v>297.073953278164</v>
+        <v>13.76</v>
       </c>
       <c r="V19" t="n">
-        <v>447.3853461641099</v>
+        <v>13.76</v>
       </c>
       <c r="W19" t="n">
-        <v>570.7662644237873</v>
+        <v>137.1409182596774</v>
       </c>
       <c r="X19" t="n">
-        <v>570.7662644237873</v>
+        <v>137.1409182596774</v>
       </c>
       <c r="Y19" t="n">
-        <v>570.7662644237873</v>
+        <v>137.1409182596774</v>
       </c>
     </row>
     <row r="20">
@@ -5719,19 +5719,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>222.0642064452536</v>
+        <v>175.3627130907006</v>
       </c>
       <c r="C20" t="n">
-        <v>222.0642064452536</v>
+        <v>175.3627130907006</v>
       </c>
       <c r="D20" t="n">
-        <v>222.0642064452536</v>
+        <v>115.4241719393372</v>
       </c>
       <c r="E20" t="n">
-        <v>168.1618937110428</v>
+        <v>61.52185920512642</v>
       </c>
       <c r="F20" t="n">
-        <v>113.7279253191116</v>
+        <v>61.52185920512642</v>
       </c>
       <c r="G20" t="n">
         <v>61.52185920512642</v>
@@ -5743,22 +5743,22 @@
         <v>15.04</v>
       </c>
       <c r="J20" t="n">
-        <v>187.1174620774201</v>
+        <v>70.53708547565205</v>
       </c>
       <c r="K20" t="n">
-        <v>322.2883856452593</v>
+        <v>256.6570854756521</v>
       </c>
       <c r="L20" t="n">
-        <v>489.9798689618422</v>
+        <v>442.777085475652</v>
       </c>
       <c r="M20" t="n">
-        <v>489.9798689618422</v>
+        <v>456.3836570592561</v>
       </c>
       <c r="N20" t="n">
-        <v>489.9798689618422</v>
+        <v>456.3836570592561</v>
       </c>
       <c r="O20" t="n">
-        <v>599.4762119025861</v>
+        <v>565.88</v>
       </c>
       <c r="P20" t="n">
         <v>752</v>
@@ -5770,25 +5770,25 @@
         <v>752</v>
       </c>
       <c r="S20" t="n">
-        <v>631.4052312437832</v>
+        <v>752</v>
       </c>
       <c r="T20" t="n">
-        <v>631.4052312437832</v>
+        <v>562.10101010101</v>
       </c>
       <c r="U20" t="n">
-        <v>441.5062413447932</v>
+        <v>562.10101010101</v>
       </c>
       <c r="V20" t="n">
-        <v>411.9631963442435</v>
+        <v>562.10101010101</v>
       </c>
       <c r="W20" t="n">
-        <v>411.9631963442435</v>
+        <v>562.10101010101</v>
       </c>
       <c r="X20" t="n">
-        <v>222.0642064452536</v>
+        <v>372.2020202020201</v>
       </c>
       <c r="Y20" t="n">
-        <v>222.0642064452536</v>
+        <v>210.2652195123167</v>
       </c>
     </row>
     <row r="21">
@@ -5807,10 +5807,10 @@
         <v>72.68362525464826</v>
       </c>
       <c r="E21" t="n">
-        <v>72.68362525464826</v>
+        <v>15.04</v>
       </c>
       <c r="F21" t="n">
-        <v>72.68362525464826</v>
+        <v>15.04</v>
       </c>
       <c r="G21" t="n">
         <v>15.04</v>
@@ -5825,19 +5825,19 @@
         <v>15.04</v>
       </c>
       <c r="K21" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="L21" t="n">
         <v>201.16</v>
       </c>
-      <c r="L21" t="n">
-        <v>379.76</v>
-      </c>
       <c r="M21" t="n">
-        <v>379.76</v>
+        <v>387.28</v>
       </c>
       <c r="N21" t="n">
-        <v>565.88</v>
+        <v>573.4</v>
       </c>
       <c r="O21" t="n">
-        <v>565.88</v>
+        <v>573.4</v>
       </c>
       <c r="P21" t="n">
         <v>752</v>
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>595.7547229912606</v>
+        <v>391.2531021698169</v>
       </c>
       <c r="C22" t="n">
-        <v>595.7547229912606</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="D22" t="n">
-        <v>595.7547229912606</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="E22" t="n">
-        <v>595.7547229912606</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="F22" t="n">
-        <v>595.7547229912606</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="G22" t="n">
-        <v>595.7547229912606</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="H22" t="n">
-        <v>720.9992547080352</v>
+        <v>468.7451079882526</v>
       </c>
       <c r="I22" t="n">
-        <v>752</v>
+        <v>634.7662644237873</v>
       </c>
       <c r="J22" t="n">
-        <v>752</v>
+        <v>634.7662644237873</v>
       </c>
       <c r="K22" t="n">
         <v>752</v>
@@ -5910,43 +5910,43 @@
         <v>751.0248829669725</v>
       </c>
       <c r="M22" t="n">
-        <v>655.915638132471</v>
+        <v>751.0248829669725</v>
       </c>
       <c r="N22" t="n">
-        <v>507.9295710423439</v>
+        <v>603.0388158768454</v>
       </c>
       <c r="O22" t="n">
-        <v>318.030581143354</v>
+        <v>413.1398259778555</v>
       </c>
       <c r="P22" t="n">
-        <v>128.131591244364</v>
+        <v>397.8507842668353</v>
       </c>
       <c r="Q22" t="n">
-        <v>15.04</v>
+        <v>207.9517943678454</v>
       </c>
       <c r="R22" t="n">
-        <v>15.04</v>
+        <v>18.05280446885548</v>
       </c>
       <c r="S22" t="n">
         <v>15.04</v>
       </c>
       <c r="T22" t="n">
-        <v>156.6423201424114</v>
+        <v>15.04</v>
       </c>
       <c r="U22" t="n">
-        <v>156.6423201424114</v>
+        <v>15.04</v>
       </c>
       <c r="V22" t="n">
-        <v>306.9537130283574</v>
+        <v>165.351392885946</v>
       </c>
       <c r="W22" t="n">
-        <v>430.3346312880348</v>
+        <v>288.7323111456234</v>
       </c>
       <c r="X22" t="n">
-        <v>532.8554223122283</v>
+        <v>391.2531021698169</v>
       </c>
       <c r="Y22" t="n">
-        <v>595.7547229912606</v>
+        <v>391.2531021698169</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>186.7678121038825</v>
+        <v>347.3101593440097</v>
       </c>
       <c r="C23" t="n">
-        <v>87.29854115136342</v>
+        <v>247.8408883914906</v>
       </c>
       <c r="D23" t="n">
-        <v>27.36</v>
+        <v>187.9023472401272</v>
       </c>
       <c r="E23" t="n">
-        <v>27.36</v>
+        <v>134.0000345059164</v>
       </c>
       <c r="F23" t="n">
-        <v>27.36</v>
+        <v>79.56606611398524</v>
       </c>
       <c r="G23" t="n">
         <v>27.36</v>
@@ -5986,19 +5986,19 @@
         <v>501.1109235678392</v>
       </c>
       <c r="L23" t="n">
-        <v>690.8400000000001</v>
+        <v>767.3998689618422</v>
       </c>
       <c r="M23" t="n">
-        <v>690.8400000000001</v>
+        <v>767.3998689618422</v>
       </c>
       <c r="N23" t="n">
-        <v>690.8400000000001</v>
+        <v>767.3998689618422</v>
       </c>
       <c r="O23" t="n">
+        <v>876.8962119025862</v>
+      </c>
+      <c r="P23" t="n">
         <v>1029.42</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1368</v>
       </c>
       <c r="Q23" t="n">
         <v>1368</v>
@@ -6007,25 +6007,25 @@
         <v>1368</v>
       </c>
       <c r="S23" t="n">
-        <v>1259.203089591667</v>
+        <v>1247.405231243783</v>
       </c>
       <c r="T23" t="n">
-        <v>1025.893070993706</v>
+        <v>1014.095212645823</v>
       </c>
       <c r="U23" t="n">
-        <v>724.7461748301943</v>
+        <v>790.9146612123232</v>
       </c>
       <c r="V23" t="n">
-        <v>724.7461748301943</v>
+        <v>509.2469600337131</v>
       </c>
       <c r="W23" t="n">
-        <v>724.7461748301943</v>
+        <v>509.2469600337131</v>
       </c>
       <c r="X23" t="n">
-        <v>481.0271511325501</v>
+        <v>509.2469600337131</v>
       </c>
       <c r="Y23" t="n">
-        <v>319.0903504428467</v>
+        <v>347.3101593440097</v>
       </c>
     </row>
     <row r="24">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>37.5619317631508</v>
+        <v>698.8855570177993</v>
       </c>
       <c r="C24" t="n">
-        <v>27.36</v>
+        <v>688.6836252546485</v>
       </c>
       <c r="D24" t="n">
-        <v>27.36</v>
+        <v>343.229079800103</v>
       </c>
       <c r="E24" t="n">
         <v>27.36</v>
@@ -6083,28 +6083,28 @@
         <v>1368</v>
       </c>
       <c r="R24" t="n">
-        <v>1152.570665285536</v>
+        <v>1205.760906108327</v>
       </c>
       <c r="S24" t="n">
-        <v>1046.614509422674</v>
+        <v>1099.804750245464</v>
       </c>
       <c r="T24" t="n">
-        <v>994.0458977106813</v>
+        <v>1047.236138533472</v>
       </c>
       <c r="U24" t="n">
-        <v>944.3766282750057</v>
+        <v>997.5668690977965</v>
       </c>
       <c r="V24" t="n">
-        <v>880.2244391926621</v>
+        <v>933.4146800154529</v>
       </c>
       <c r="W24" t="n">
-        <v>798.0293453443504</v>
+        <v>851.2195861671412</v>
       </c>
       <c r="X24" t="n">
-        <v>728.4710226722418</v>
+        <v>781.6612634950326</v>
       </c>
       <c r="Y24" t="n">
-        <v>383.0164772176963</v>
+        <v>732.7810687817656</v>
       </c>
     </row>
     <row r="25">
@@ -6114,22 +6114,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>319.2737130283573</v>
+        <v>474.6857962400936</v>
       </c>
       <c r="C25" t="n">
-        <v>396.7657188467931</v>
+        <v>474.6857962400936</v>
       </c>
       <c r="D25" t="n">
-        <v>461.5748629717932</v>
+        <v>474.6857962400936</v>
       </c>
       <c r="E25" t="n">
-        <v>530.8937671832063</v>
+        <v>544.0047004515067</v>
       </c>
       <c r="F25" t="n">
-        <v>606.7447397751417</v>
+        <v>619.8556730434422</v>
       </c>
       <c r="G25" t="n">
-        <v>712.1179663177647</v>
+        <v>725.2288995860652</v>
       </c>
       <c r="H25" t="n">
         <v>725.2288995860652</v>
@@ -6168,22 +6168,22 @@
         <v>27.36</v>
       </c>
       <c r="T25" t="n">
-        <v>168.9623201424114</v>
+        <v>27.36</v>
       </c>
       <c r="U25" t="n">
-        <v>168.9623201424114</v>
+        <v>122.6374486108983</v>
       </c>
       <c r="V25" t="n">
-        <v>319.2737130283573</v>
+        <v>122.6374486108983</v>
       </c>
       <c r="W25" t="n">
-        <v>319.2737130283573</v>
+        <v>246.0183668705757</v>
       </c>
       <c r="X25" t="n">
-        <v>319.2737130283573</v>
+        <v>348.5391578947692</v>
       </c>
       <c r="Y25" t="n">
-        <v>319.2737130283573</v>
+        <v>411.4384585738015</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>456.154507768541</v>
+        <v>562.10101010101</v>
       </c>
       <c r="C26" t="n">
-        <v>280.9276610584461</v>
+        <v>386.8741633909152</v>
       </c>
       <c r="D26" t="n">
-        <v>145.2315441495069</v>
+        <v>386.8741633909152</v>
       </c>
       <c r="E26" t="n">
-        <v>145.2315441495069</v>
+        <v>386.8741633909152</v>
       </c>
       <c r="F26" t="n">
-        <v>15.04</v>
+        <v>256.6826192414082</v>
       </c>
       <c r="G26" t="n">
-        <v>15.04</v>
+        <v>137.2794349627022</v>
       </c>
       <c r="H26" t="n">
         <v>15.04</v>
@@ -6217,25 +6217,25 @@
         <v>15.04</v>
       </c>
       <c r="J26" t="n">
-        <v>70.53708547565205</v>
+        <v>187.1174620774201</v>
       </c>
       <c r="K26" t="n">
-        <v>205.7080090434912</v>
+        <v>322.2883856452593</v>
       </c>
       <c r="L26" t="n">
-        <v>373.3994923600741</v>
+        <v>489.9798689618422</v>
       </c>
       <c r="M26" t="n">
-        <v>373.3994923600741</v>
+        <v>489.9798689618422</v>
       </c>
       <c r="N26" t="n">
-        <v>373.3994923600741</v>
+        <v>489.9798689618422</v>
       </c>
       <c r="O26" t="n">
-        <v>482.8958353008181</v>
+        <v>599.4762119025861</v>
       </c>
       <c r="P26" t="n">
-        <v>635.4196233982319</v>
+        <v>752</v>
       </c>
       <c r="Q26" t="n">
         <v>752</v>
@@ -6256,13 +6256,13 @@
         <v>752</v>
       </c>
       <c r="W26" t="n">
-        <v>562.10101010101</v>
+        <v>752</v>
       </c>
       <c r="X26" t="n">
-        <v>456.154507768541</v>
+        <v>752</v>
       </c>
       <c r="Y26" t="n">
-        <v>456.154507768541</v>
+        <v>752</v>
       </c>
     </row>
     <row r="27">
@@ -6272,16 +6272,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>252.3725319744445</v>
+        <v>305.288423134355</v>
       </c>
       <c r="C27" t="n">
-        <v>166.4130244537179</v>
+        <v>219.3289156136284</v>
       </c>
       <c r="D27" t="n">
-        <v>93.74869425401829</v>
+        <v>146.6645854139288</v>
       </c>
       <c r="E27" t="n">
-        <v>26.4031415046116</v>
+        <v>79.3190326645221</v>
       </c>
       <c r="F27" t="n">
         <v>15.04</v>
@@ -6296,19 +6296,19 @@
         <v>15.04</v>
       </c>
       <c r="J27" t="n">
-        <v>15.04</v>
+        <v>192.7128647979405</v>
       </c>
       <c r="K27" t="n">
-        <v>15.04</v>
+        <v>378.8328647979405</v>
       </c>
       <c r="L27" t="n">
-        <v>193.64</v>
+        <v>389.4244743356763</v>
       </c>
       <c r="M27" t="n">
-        <v>193.64</v>
+        <v>565.88</v>
       </c>
       <c r="N27" t="n">
-        <v>379.76</v>
+        <v>565.88</v>
       </c>
       <c r="O27" t="n">
         <v>565.88</v>
@@ -6326,22 +6326,22 @@
         <v>752</v>
       </c>
       <c r="T27" t="n">
-        <v>752</v>
+        <v>623.673812530432</v>
       </c>
       <c r="U27" t="n">
-        <v>626.5731548067487</v>
+        <v>590.5140864039587</v>
       </c>
       <c r="V27" t="n">
-        <v>486.6633899668293</v>
+        <v>450.6043215640394</v>
       </c>
       <c r="W27" t="n">
-        <v>486.6633899668293</v>
+        <v>450.6043215640394</v>
       </c>
       <c r="X27" t="n">
-        <v>486.6633899668293</v>
+        <v>305.288423134355</v>
       </c>
       <c r="Y27" t="n">
-        <v>362.0256194959865</v>
+        <v>305.288423134355</v>
       </c>
     </row>
     <row r="28">
@@ -6396,10 +6396,10 @@
         <v>123.5759725872521</v>
       </c>
       <c r="Q28" t="n">
-        <v>15.04</v>
+        <v>123.5759725872521</v>
       </c>
       <c r="R28" t="n">
-        <v>15.04</v>
+        <v>93.81038022643123</v>
       </c>
       <c r="S28" t="n">
         <v>15.04</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13.84</v>
+        <v>321.3192007644203</v>
       </c>
       <c r="C29" t="n">
-        <v>13.84</v>
+        <v>222.8600308220022</v>
       </c>
       <c r="D29" t="n">
-        <v>13.84</v>
+        <v>163.9315906807398</v>
       </c>
       <c r="E29" t="n">
-        <v>13.84</v>
+        <v>163.9315906807398</v>
       </c>
       <c r="F29" t="n">
-        <v>13.84</v>
+        <v>110.5077232989096</v>
       </c>
       <c r="G29" t="n">
-        <v>13.84</v>
+        <v>59.3117581950254</v>
       </c>
       <c r="H29" t="n">
         <v>13.84</v>
@@ -6454,25 +6454,25 @@
         <v>13.84</v>
       </c>
       <c r="J29" t="n">
-        <v>127.11746207742</v>
+        <v>69.33708547565205</v>
       </c>
       <c r="K29" t="n">
-        <v>262.2883856452593</v>
+        <v>204.5080090434912</v>
       </c>
       <c r="L29" t="n">
-        <v>429.9798689618422</v>
+        <v>372.1994923600741</v>
       </c>
       <c r="M29" t="n">
-        <v>429.9798689618422</v>
+        <v>372.1994923600742</v>
       </c>
       <c r="N29" t="n">
-        <v>429.9798689618422</v>
+        <v>372.1994923600742</v>
       </c>
       <c r="O29" t="n">
-        <v>539.4762119025861</v>
+        <v>481.6958353008181</v>
       </c>
       <c r="P29" t="n">
-        <v>692</v>
+        <v>634.219623398232</v>
       </c>
       <c r="Q29" t="n">
         <v>692</v>
@@ -6484,22 +6484,22 @@
         <v>692</v>
       </c>
       <c r="T29" t="n">
-        <v>538.0824242424244</v>
+        <v>670.8141502593699</v>
       </c>
       <c r="U29" t="n">
-        <v>538.0824242424244</v>
+        <v>496.066675511895</v>
       </c>
       <c r="V29" t="n">
-        <v>363.3349494949496</v>
+        <v>321.3192007644203</v>
       </c>
       <c r="W29" t="n">
-        <v>188.5874747474748</v>
+        <v>321.3192007644203</v>
       </c>
       <c r="X29" t="n">
-        <v>13.84</v>
+        <v>321.3192007644203</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.84</v>
+        <v>321.3192007644203</v>
       </c>
     </row>
     <row r="30">
@@ -6527,7 +6527,7 @@
         <v>22.78463535565832</v>
       </c>
       <c r="H30" t="n">
-        <v>13.84</v>
+        <v>22.78463535565832</v>
       </c>
       <c r="I30" t="n">
         <v>13.84</v>
@@ -6536,19 +6536,19 @@
         <v>185.11</v>
       </c>
       <c r="K30" t="n">
-        <v>185.11</v>
+        <v>356.38</v>
       </c>
       <c r="L30" t="n">
-        <v>356.38</v>
+        <v>366.9716095377358</v>
       </c>
       <c r="M30" t="n">
-        <v>356.38</v>
+        <v>366.9716095377358</v>
       </c>
       <c r="N30" t="n">
-        <v>527.65</v>
+        <v>366.9716095377358</v>
       </c>
       <c r="O30" t="n">
-        <v>687.8600532715052</v>
+        <v>520.73</v>
       </c>
       <c r="P30" t="n">
         <v>692</v>
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>288.6207910241935</v>
+        <v>299.5735896686989</v>
       </c>
       <c r="C31" t="n">
-        <v>288.6207910241935</v>
+        <v>378.0555954871347</v>
       </c>
       <c r="D31" t="n">
-        <v>288.6207910241935</v>
+        <v>443.8547396121347</v>
       </c>
       <c r="E31" t="n">
-        <v>288.6207910241935</v>
+        <v>443.8547396121347</v>
       </c>
       <c r="F31" t="n">
-        <v>288.6207910241935</v>
+        <v>520.6957122040702</v>
       </c>
       <c r="G31" t="n">
-        <v>288.6207910241935</v>
+        <v>520.6957122040702</v>
       </c>
       <c r="H31" t="n">
-        <v>414.8553227409681</v>
+        <v>520.6957122040702</v>
       </c>
       <c r="I31" t="n">
-        <v>573.7419766278575</v>
+        <v>691.9657122040702</v>
       </c>
       <c r="J31" t="n">
-        <v>573.7419766278575</v>
+        <v>691.9657122040702</v>
       </c>
       <c r="K31" t="n">
         <v>691.9657122040702</v>
@@ -6627,13 +6627,13 @@
         <v>450.9248900955734</v>
       </c>
       <c r="O31" t="n">
-        <v>276.1774153480986</v>
+        <v>450.9248900955734</v>
       </c>
       <c r="P31" t="n">
-        <v>101.4299406006239</v>
+        <v>365.337652953704</v>
       </c>
       <c r="Q31" t="n">
-        <v>15.84270345875446</v>
+        <v>190.5901782062292</v>
       </c>
       <c r="R31" t="n">
         <v>15.84270345875446</v>
@@ -6645,19 +6645,19 @@
         <v>13.84</v>
       </c>
       <c r="U31" t="n">
-        <v>185.11</v>
+        <v>175.2026714090215</v>
       </c>
       <c r="V31" t="n">
-        <v>185.11</v>
+        <v>175.2026714090215</v>
       </c>
       <c r="W31" t="n">
-        <v>185.11</v>
+        <v>299.5735896686989</v>
       </c>
       <c r="X31" t="n">
-        <v>288.6207910241935</v>
+        <v>299.5735896686989</v>
       </c>
       <c r="Y31" t="n">
-        <v>288.6207910241935</v>
+        <v>299.5735896686989</v>
       </c>
     </row>
     <row r="32">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>71.40308312901436</v>
+        <v>63.98979450290346</v>
       </c>
       <c r="C32" t="n">
-        <v>24.45906470174777</v>
+        <v>17.04577607563687</v>
       </c>
       <c r="D32" t="n">
         <v>17.04577607563687</v>
@@ -6697,16 +6697,16 @@
         <v>239.537085475652</v>
       </c>
       <c r="L32" t="n">
-        <v>407.228568792235</v>
+        <v>408.2236570592561</v>
       </c>
       <c r="M32" t="n">
-        <v>425.9798689618422</v>
+        <v>408.2236570592561</v>
       </c>
       <c r="N32" t="n">
-        <v>425.9798689618422</v>
+        <v>408.2236570592561</v>
       </c>
       <c r="O32" t="n">
-        <v>535.4762119025861</v>
+        <v>517.72</v>
       </c>
       <c r="P32" t="n">
         <v>688</v>
@@ -6721,22 +6721,22 @@
         <v>688</v>
       </c>
       <c r="T32" t="n">
-        <v>514.2626262626262</v>
+        <v>520.8760901421019</v>
       </c>
       <c r="U32" t="n">
-        <v>514.2626262626262</v>
+        <v>520.8760901421019</v>
       </c>
       <c r="V32" t="n">
-        <v>514.2626262626262</v>
+        <v>347.1387164047281</v>
       </c>
       <c r="W32" t="n">
-        <v>434.3492908445506</v>
+        <v>173.4013426673544</v>
       </c>
       <c r="X32" t="n">
-        <v>260.6119171071769</v>
+        <v>173.4013426673544</v>
       </c>
       <c r="Y32" t="n">
-        <v>151.200368942726</v>
+        <v>63.98979450290346</v>
       </c>
     </row>
     <row r="33">
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="C33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="D33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="E33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="F33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="G33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="H33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="I33" t="n">
         <v>13.76</v>
@@ -6776,46 +6776,46 @@
         <v>13.76</v>
       </c>
       <c r="L33" t="n">
-        <v>177.1600000000001</v>
+        <v>184.04</v>
       </c>
       <c r="M33" t="n">
-        <v>177.1600000000001</v>
+        <v>354.32</v>
       </c>
       <c r="N33" t="n">
-        <v>347.4400000000001</v>
+        <v>524.6</v>
       </c>
       <c r="O33" t="n">
-        <v>517.72</v>
+        <v>683.8600532715052</v>
       </c>
       <c r="P33" t="n">
         <v>688</v>
       </c>
       <c r="Q33" t="n">
-        <v>587.2220878636284</v>
+        <v>688</v>
       </c>
       <c r="R33" t="n">
-        <v>472.9954988393638</v>
+        <v>578.2861586335791</v>
       </c>
       <c r="S33" t="n">
-        <v>419.5645955017538</v>
+        <v>524.8552552959691</v>
       </c>
       <c r="T33" t="n">
-        <v>245.82722176438</v>
+        <v>524.8118961092333</v>
       </c>
       <c r="U33" t="n">
-        <v>245.82722176438</v>
+        <v>524.8118961092333</v>
       </c>
       <c r="V33" t="n">
-        <v>234.200285207289</v>
+        <v>351.0745223718595</v>
       </c>
       <c r="W33" t="n">
-        <v>204.5304438842299</v>
+        <v>177.3371486344858</v>
       </c>
       <c r="X33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
       <c r="Y33" t="n">
-        <v>187.4973737373737</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="34">
@@ -6825,34 +6825,34 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="C34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="D34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="E34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="F34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="G34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
       <c r="H34" t="n">
-        <v>184.04</v>
+        <v>688</v>
       </c>
       <c r="I34" t="n">
-        <v>298.4819766278575</v>
+        <v>688</v>
       </c>
       <c r="J34" t="n">
-        <v>468.7619766278576</v>
+        <v>688</v>
       </c>
       <c r="K34" t="n">
-        <v>637.4757122040702</v>
+        <v>688</v>
       </c>
       <c r="L34" t="n">
         <v>688</v>
@@ -6879,22 +6879,22 @@
         <v>13.76</v>
       </c>
       <c r="T34" t="n">
-        <v>13.76</v>
+        <v>79.05990829677427</v>
       </c>
       <c r="U34" t="n">
-        <v>13.76</v>
+        <v>249.3399082967743</v>
       </c>
       <c r="V34" t="n">
-        <v>13.76</v>
+        <v>419.6199082967743</v>
       </c>
       <c r="W34" t="n">
-        <v>13.76</v>
+        <v>419.6199082967743</v>
       </c>
       <c r="X34" t="n">
-        <v>13.76</v>
+        <v>573.6206993209678</v>
       </c>
       <c r="Y34" t="n">
-        <v>13.76</v>
+        <v>688</v>
       </c>
     </row>
     <row r="35">
@@ -6904,10 +6904,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.29906470174777</v>
+        <v>63.82979450290345</v>
       </c>
       <c r="C35" t="n">
-        <v>24.29906470174777</v>
+        <v>16.88577607563687</v>
       </c>
       <c r="D35" t="n">
         <v>16.88577607563687</v>
@@ -6931,22 +6931,22 @@
         <v>69.09708547565204</v>
       </c>
       <c r="K35" t="n">
-        <v>237.397085475652</v>
+        <v>204.2680090434912</v>
       </c>
       <c r="L35" t="n">
-        <v>405.088568792235</v>
+        <v>371.9594923600742</v>
       </c>
       <c r="M35" t="n">
-        <v>417.9798689618422</v>
+        <v>371.9594923600743</v>
       </c>
       <c r="N35" t="n">
-        <v>417.9798689618422</v>
+        <v>371.9594923600743</v>
       </c>
       <c r="O35" t="n">
-        <v>527.4762119025861</v>
+        <v>481.4558353008182</v>
       </c>
       <c r="P35" t="n">
-        <v>680</v>
+        <v>633.979623398232</v>
       </c>
       <c r="Q35" t="n">
         <v>680</v>
@@ -6958,22 +6958,22 @@
         <v>680</v>
       </c>
       <c r="T35" t="n">
-        <v>539.450579853263</v>
+        <v>578.9813096544186</v>
       </c>
       <c r="U35" t="n">
-        <v>367.7334081360913</v>
+        <v>407.2641379372469</v>
       </c>
       <c r="V35" t="n">
-        <v>196.0162364189195</v>
+        <v>235.5469662200752</v>
       </c>
       <c r="W35" t="n">
-        <v>24.29906470174777</v>
+        <v>235.5469662200752</v>
       </c>
       <c r="X35" t="n">
-        <v>24.29906470174777</v>
+        <v>63.82979450290345</v>
       </c>
       <c r="Y35" t="n">
-        <v>24.29906470174777</v>
+        <v>63.82979450290345</v>
       </c>
     </row>
     <row r="36">
@@ -6983,46 +6983,46 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>126.674641204974</v>
+        <v>185.3171717171717</v>
       </c>
       <c r="C36" t="n">
-        <v>126.674641204974</v>
+        <v>185.3171717171717</v>
       </c>
       <c r="D36" t="n">
-        <v>126.674641204974</v>
+        <v>13.6</v>
       </c>
       <c r="E36" t="n">
-        <v>126.674641204974</v>
+        <v>13.6</v>
       </c>
       <c r="F36" t="n">
-        <v>126.674641204974</v>
+        <v>13.6</v>
       </c>
       <c r="G36" t="n">
-        <v>126.674641204974</v>
+        <v>13.6</v>
       </c>
       <c r="H36" t="n">
-        <v>126.674641204974</v>
+        <v>13.6</v>
       </c>
       <c r="I36" t="n">
         <v>13.6</v>
       </c>
       <c r="J36" t="n">
-        <v>13.6</v>
+        <v>181.9</v>
       </c>
       <c r="K36" t="n">
-        <v>181.9</v>
+        <v>350.2</v>
       </c>
       <c r="L36" t="n">
-        <v>192.4916095377359</v>
+        <v>360.7916095377359</v>
       </c>
       <c r="M36" t="n">
-        <v>192.4916095377359</v>
+        <v>529.0916095377358</v>
       </c>
       <c r="N36" t="n">
-        <v>343.4</v>
+        <v>675.8600532715052</v>
       </c>
       <c r="O36" t="n">
-        <v>511.7</v>
+        <v>675.8600532715052</v>
       </c>
       <c r="P36" t="n">
         <v>680</v>
@@ -7034,25 +7034,25 @@
         <v>570.2861586335791</v>
       </c>
       <c r="S36" t="n">
-        <v>516.8552552959691</v>
+        <v>398.5689869164074</v>
       </c>
       <c r="T36" t="n">
-        <v>516.8118961092326</v>
+        <v>398.5256277296714</v>
       </c>
       <c r="U36" t="n">
-        <v>345.0947243920609</v>
+        <v>243.647019744178</v>
       </c>
       <c r="V36" t="n">
-        <v>173.3775526748892</v>
+        <v>232.020083187087</v>
       </c>
       <c r="W36" t="n">
-        <v>143.7077113518301</v>
+        <v>202.3502418640279</v>
       </c>
       <c r="X36" t="n">
-        <v>126.674641204974</v>
+        <v>185.3171717171717</v>
       </c>
       <c r="Y36" t="n">
-        <v>126.674641204974</v>
+        <v>185.3171717171717</v>
       </c>
     </row>
     <row r="37">
@@ -7062,49 +7062,49 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="C37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="D37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="E37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="F37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="G37" t="n">
-        <v>292.8757122040702</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="H37" t="n">
-        <v>461.1757122040702</v>
+        <v>680</v>
       </c>
       <c r="I37" t="n">
-        <v>629.4757122040702</v>
+        <v>680</v>
       </c>
       <c r="J37" t="n">
-        <v>629.4757122040702</v>
+        <v>680</v>
       </c>
       <c r="K37" t="n">
-        <v>629.4757122040702</v>
+        <v>680</v>
       </c>
       <c r="L37" t="n">
         <v>680</v>
       </c>
       <c r="M37" t="n">
-        <v>637.416007690751</v>
+        <v>680</v>
       </c>
       <c r="N37" t="n">
-        <v>541.9551931258765</v>
+        <v>584.5391854351254</v>
       </c>
       <c r="O37" t="n">
-        <v>370.8529674457984</v>
+        <v>413.4369597550474</v>
       </c>
       <c r="P37" t="n">
-        <v>357.0343434343434</v>
+        <v>241.7197880378756</v>
       </c>
       <c r="Q37" t="n">
         <v>185.3171717171717</v>
@@ -7116,22 +7116,22 @@
         <v>62.12715034007474</v>
       </c>
       <c r="T37" t="n">
-        <v>136.0224856614472</v>
+        <v>230.4271503400747</v>
       </c>
       <c r="U37" t="n">
-        <v>136.0224856614472</v>
+        <v>398.7271503400748</v>
       </c>
       <c r="V37" t="n">
-        <v>136.0224856614472</v>
+        <v>398.7271503400748</v>
       </c>
       <c r="W37" t="n">
-        <v>136.0224856614472</v>
+        <v>398.7271503400748</v>
       </c>
       <c r="X37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
       <c r="Y37" t="n">
-        <v>136.0224856614472</v>
+        <v>552.7279413642683</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>13.6</v>
       </c>
       <c r="J38" t="n">
-        <v>69.09708547565204</v>
+        <v>115.11746207742</v>
       </c>
       <c r="K38" t="n">
-        <v>237.397085475652</v>
+        <v>250.2883856452592</v>
       </c>
       <c r="L38" t="n">
-        <v>405.0885687922351</v>
+        <v>417.9798689618422</v>
       </c>
       <c r="M38" t="n">
-        <v>405.0885687922352</v>
+        <v>417.9798689618422</v>
       </c>
       <c r="N38" t="n">
-        <v>405.0885687922352</v>
+        <v>417.9798689618422</v>
       </c>
       <c r="O38" t="n">
-        <v>514.5849117329791</v>
+        <v>527.4762119025861</v>
       </c>
       <c r="P38" t="n">
-        <v>667.1086998303929</v>
+        <v>680</v>
       </c>
       <c r="Q38" t="n">
         <v>680</v>
@@ -7192,25 +7192,25 @@
         <v>680</v>
       </c>
       <c r="S38" t="n">
-        <v>680</v>
+        <v>611.9304837690357</v>
       </c>
       <c r="T38" t="n">
-        <v>680</v>
+        <v>440.213312051864</v>
       </c>
       <c r="U38" t="n">
-        <v>524.0889747278087</v>
+        <v>268.4961403346923</v>
       </c>
       <c r="V38" t="n">
-        <v>352.371803010637</v>
+        <v>268.4961403346923</v>
       </c>
       <c r="W38" t="n">
-        <v>180.6546312934653</v>
+        <v>268.4961403346923</v>
       </c>
       <c r="X38" t="n">
-        <v>180.6546312934653</v>
+        <v>260.4519171071769</v>
       </c>
       <c r="Y38" t="n">
-        <v>71.24308312901435</v>
+        <v>151.040368942726</v>
       </c>
     </row>
     <row r="39">
@@ -7220,43 +7220,43 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="C39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="D39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="E39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="F39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="G39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
       <c r="H39" t="n">
-        <v>115.0477046478827</v>
+        <v>115.0910638346193</v>
       </c>
       <c r="I39" t="n">
         <v>13.6</v>
       </c>
       <c r="J39" t="n">
-        <v>13.6</v>
+        <v>181.9</v>
       </c>
       <c r="K39" t="n">
-        <v>181.9</v>
+        <v>350.2</v>
       </c>
       <c r="L39" t="n">
-        <v>350.2</v>
+        <v>511.7</v>
       </c>
       <c r="M39" t="n">
-        <v>350.2</v>
+        <v>511.7</v>
       </c>
       <c r="N39" t="n">
-        <v>350.2</v>
+        <v>511.7</v>
       </c>
       <c r="O39" t="n">
         <v>511.7</v>
@@ -7274,22 +7274,22 @@
         <v>516.8552552959691</v>
       </c>
       <c r="T39" t="n">
-        <v>516.8118961092325</v>
+        <v>345.1380835787974</v>
       </c>
       <c r="U39" t="n">
-        <v>516.8118961092325</v>
+        <v>345.1380835787974</v>
       </c>
       <c r="V39" t="n">
-        <v>505.1849595521414</v>
+        <v>333.5111470217063</v>
       </c>
       <c r="W39" t="n">
-        <v>475.5151182290823</v>
+        <v>303.8413056986471</v>
       </c>
       <c r="X39" t="n">
-        <v>458.4820480822262</v>
+        <v>286.808235551791</v>
       </c>
       <c r="Y39" t="n">
-        <v>286.7648763650544</v>
+        <v>286.808235551791</v>
       </c>
     </row>
     <row r="40">
@@ -7299,28 +7299,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>504.2007910241936</v>
+        <v>343.4</v>
       </c>
       <c r="C40" t="n">
-        <v>504.2007910241936</v>
+        <v>343.4</v>
       </c>
       <c r="D40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="E40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="F40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="G40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="H40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="I40" t="n">
-        <v>511.7</v>
+        <v>343.4</v>
       </c>
       <c r="J40" t="n">
         <v>511.7</v>
@@ -7332,16 +7332,16 @@
         <v>680</v>
       </c>
       <c r="M40" t="n">
-        <v>680</v>
+        <v>637.416007690751</v>
       </c>
       <c r="N40" t="n">
-        <v>584.5391854351254</v>
+        <v>541.9551931258765</v>
       </c>
       <c r="O40" t="n">
-        <v>413.4369597550474</v>
+        <v>528.7515151515152</v>
       </c>
       <c r="P40" t="n">
-        <v>241.7197880378756</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="Q40" t="n">
         <v>185.3171717171717</v>
@@ -7350,25 +7350,25 @@
         <v>13.6</v>
       </c>
       <c r="S40" t="n">
-        <v>13.6</v>
+        <v>62.12715034007474</v>
       </c>
       <c r="T40" t="n">
-        <v>13.6</v>
+        <v>230.4271503400747</v>
       </c>
       <c r="U40" t="n">
-        <v>13.6</v>
+        <v>343.4</v>
       </c>
       <c r="V40" t="n">
-        <v>181.9</v>
+        <v>343.4</v>
       </c>
       <c r="W40" t="n">
-        <v>350.2</v>
+        <v>343.4</v>
       </c>
       <c r="X40" t="n">
-        <v>504.2007910241936</v>
+        <v>343.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>504.2007910241936</v>
+        <v>343.4</v>
       </c>
     </row>
     <row r="41">
@@ -7381,16 +7381,16 @@
         <v>357.0343434343434</v>
       </c>
       <c r="C41" t="n">
+        <v>357.0343434343434</v>
+      </c>
+      <c r="D41" t="n">
+        <v>357.0343434343434</v>
+      </c>
+      <c r="E41" t="n">
+        <v>357.0343434343434</v>
+      </c>
+      <c r="F41" t="n">
         <v>185.3171717171717</v>
-      </c>
-      <c r="D41" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="E41" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F41" t="n">
-        <v>13.6</v>
       </c>
       <c r="G41" t="n">
         <v>13.6</v>
@@ -7408,16 +7408,16 @@
         <v>237.397085475652</v>
       </c>
       <c r="L41" t="n">
-        <v>405.0885687922351</v>
+        <v>405.088568792235</v>
       </c>
       <c r="M41" t="n">
-        <v>405.0885687922352</v>
+        <v>405.088568792235</v>
       </c>
       <c r="N41" t="n">
-        <v>405.0885687922352</v>
+        <v>405.088568792235</v>
       </c>
       <c r="O41" t="n">
-        <v>514.5849117329791</v>
+        <v>514.584911732979</v>
       </c>
       <c r="P41" t="n">
         <v>667.1086998303929</v>
@@ -7429,25 +7429,25 @@
         <v>680</v>
       </c>
       <c r="S41" t="n">
-        <v>680</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="T41" t="n">
-        <v>680</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="U41" t="n">
-        <v>680</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="V41" t="n">
-        <v>680</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="W41" t="n">
-        <v>680</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="X41" t="n">
-        <v>680</v>
+        <v>357.0343434343434</v>
       </c>
       <c r="Y41" t="n">
-        <v>528.7515151515152</v>
+        <v>357.0343434343434</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>13.6</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="C42" t="n">
-        <v>13.6</v>
+        <v>351.616250055031</v>
       </c>
       <c r="D42" t="n">
-        <v>13.6</v>
+        <v>351.616250055031</v>
       </c>
       <c r="E42" t="n">
-        <v>13.6</v>
+        <v>213.5636265985536</v>
       </c>
       <c r="F42" t="n">
-        <v>13.6</v>
+        <v>213.5636265985536</v>
       </c>
       <c r="G42" t="n">
-        <v>13.6</v>
+        <v>135.439939410717</v>
       </c>
       <c r="H42" t="n">
         <v>13.6</v>
@@ -7481,7 +7481,7 @@
         <v>13.6</v>
       </c>
       <c r="J42" t="n">
-        <v>13.6</v>
+        <v>181.9</v>
       </c>
       <c r="K42" t="n">
         <v>181.9</v>
@@ -7505,28 +7505,28 @@
         <v>680</v>
       </c>
       <c r="R42" t="n">
+        <v>680</v>
+      </c>
+      <c r="S42" t="n">
+        <v>680</v>
+      </c>
+      <c r="T42" t="n">
+        <v>680</v>
+      </c>
+      <c r="U42" t="n">
         <v>508.2828282828283</v>
       </c>
-      <c r="S42" t="n">
-        <v>357.0343434343434</v>
-      </c>
-      <c r="T42" t="n">
-        <v>357.0343434343434</v>
-      </c>
-      <c r="U42" t="n">
-        <v>357.0343434343434</v>
-      </c>
       <c r="V42" t="n">
-        <v>185.3171717171717</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="W42" t="n">
-        <v>13.6</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="X42" t="n">
-        <v>13.6</v>
+        <v>508.2828282828283</v>
       </c>
       <c r="Y42" t="n">
-        <v>13.6</v>
+        <v>508.2828282828283</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="C43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="D43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="E43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="F43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="G43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="H43" t="n">
+        <v>54.29998939968731</v>
+      </c>
+      <c r="I43" t="n">
+        <v>97.70735423740958</v>
+      </c>
+      <c r="J43" t="n">
+        <v>266.0073542374096</v>
+      </c>
+      <c r="K43" t="n">
+        <v>266.0073542374096</v>
+      </c>
+      <c r="L43" t="n">
+        <v>266.0073542374096</v>
+      </c>
+      <c r="M43" t="n">
+        <v>94.29018252023783</v>
+      </c>
+      <c r="N43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="O43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="P43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="R43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15.58722564798346</v>
+      </c>
+      <c r="T43" t="n">
         <v>13.6</v>
       </c>
-      <c r="I43" t="n">
-        <v>57.00736483772227</v>
-      </c>
-      <c r="J43" t="n">
-        <v>225.3073648377223</v>
-      </c>
-      <c r="K43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="L43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="M43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="N43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="O43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="P43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="R43" t="n">
-        <v>198.456773649285</v>
-      </c>
-      <c r="S43" t="n">
-        <v>48.97932271578304</v>
-      </c>
-      <c r="T43" t="n">
-        <v>46.99209706779958</v>
-      </c>
       <c r="U43" t="n">
-        <v>101.5092893782174</v>
+        <v>68.11719231041779</v>
       </c>
       <c r="V43" t="n">
-        <v>108.2706822641633</v>
+        <v>74.87858519636376</v>
       </c>
       <c r="W43" t="n">
-        <v>87.69208646748689</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="X43" t="n">
-        <v>45.82981835626714</v>
+        <v>54.29998939968731</v>
       </c>
       <c r="Y43" t="n">
-        <v>32.2771434376343</v>
+        <v>54.29998939968731</v>
       </c>
     </row>
     <row r="44">
@@ -7615,13 +7615,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>460.4444444444445</v>
+        <v>225.1484695033462</v>
       </c>
       <c r="C44" t="n">
-        <v>304.8888888888889</v>
+        <v>225.1484695033462</v>
       </c>
       <c r="D44" t="n">
-        <v>225.1484695033462</v>
+        <v>69.59291394779065</v>
       </c>
       <c r="E44" t="n">
         <v>69.59291394779065</v>
@@ -7663,28 +7663,28 @@
         <v>616</v>
       </c>
       <c r="R44" t="n">
-        <v>616</v>
+        <v>483.2184652208995</v>
       </c>
       <c r="S44" t="n">
-        <v>616</v>
+        <v>483.2184652208995</v>
       </c>
       <c r="T44" t="n">
-        <v>616</v>
+        <v>483.2184652208995</v>
       </c>
       <c r="U44" t="n">
-        <v>460.4444444444445</v>
+        <v>483.2184652208995</v>
       </c>
       <c r="V44" t="n">
-        <v>460.4444444444445</v>
+        <v>327.6629096653439</v>
       </c>
       <c r="W44" t="n">
-        <v>460.4444444444445</v>
+        <v>327.6629096653439</v>
       </c>
       <c r="X44" t="n">
-        <v>460.4444444444445</v>
+        <v>225.1484695033462</v>
       </c>
       <c r="Y44" t="n">
-        <v>460.4444444444445</v>
+        <v>225.1484695033462</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>460.4444444444445</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="C45" t="n">
-        <v>304.8888888888889</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="D45" t="n">
-        <v>304.8888888888889</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="E45" t="n">
-        <v>304.8888888888889</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="F45" t="n">
-        <v>159.1414875593953</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="G45" t="n">
-        <v>159.1414875593953</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="H45" t="n">
-        <v>159.1414875593953</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="I45" t="n">
         <v>12.32</v>
@@ -7721,16 +7721,16 @@
         <v>12.32</v>
       </c>
       <c r="K45" t="n">
-        <v>158.6199999999999</v>
+        <v>164.78</v>
       </c>
       <c r="L45" t="n">
-        <v>311.0799999999999</v>
+        <v>317.24</v>
       </c>
       <c r="M45" t="n">
-        <v>311.0799999999999</v>
+        <v>317.24</v>
       </c>
       <c r="N45" t="n">
-        <v>311.0799999999999</v>
+        <v>317.24</v>
       </c>
       <c r="O45" t="n">
         <v>463.54</v>
@@ -7739,31 +7739,31 @@
         <v>616</v>
       </c>
       <c r="Q45" t="n">
-        <v>616</v>
+        <v>567.747340388881</v>
       </c>
       <c r="R45" t="n">
-        <v>616</v>
+        <v>412.1917848333254</v>
       </c>
       <c r="S45" t="n">
-        <v>616</v>
+        <v>256.6362292777699</v>
       </c>
       <c r="T45" t="n">
-        <v>616</v>
+        <v>256.6362292777699</v>
       </c>
       <c r="U45" t="n">
-        <v>616</v>
+        <v>256.6362292777699</v>
       </c>
       <c r="V45" t="n">
-        <v>616</v>
+        <v>256.6362292777699</v>
       </c>
       <c r="W45" t="n">
-        <v>616</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="X45" t="n">
-        <v>460.4444444444445</v>
+        <v>101.0806737222143</v>
       </c>
       <c r="Y45" t="n">
-        <v>460.4444444444445</v>
+        <v>101.0806737222143</v>
       </c>
     </row>
     <row r="46">
@@ -7830,7 +7830,7 @@
         <v>62.58364901310703</v>
       </c>
       <c r="U46" t="n">
-        <v>12.32</v>
+        <v>62.58364901310703</v>
       </c>
       <c r="V46" t="n">
         <v>12.32</v>
@@ -8049,10 +8049,10 @@
         <v>12.03922584486371</v>
       </c>
       <c r="L3" t="n">
-        <v>143.3014045073375</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>382.825791671164</v>
+        <v>376.3089605507184</v>
       </c>
       <c r="N3" t="n">
         <v>355.4156280060917</v>
@@ -8061,7 +8061,7 @@
         <v>4.583748596270539</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>149.818235627783</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8280,22 +8280,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>216.9972017278486</v>
+        <v>47.99720172784856</v>
       </c>
       <c r="K6" t="n">
-        <v>163.5123475239184</v>
+        <v>181.0392258448637</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>151.4731216790547</v>
       </c>
       <c r="M6" t="n">
         <v>239.2297782656032</v>
       </c>
       <c r="N6" t="n">
-        <v>201.4156280060917</v>
+        <v>370.4156280060917</v>
       </c>
       <c r="O6" t="n">
-        <v>173.5837485962705</v>
+        <v>4.583748596270539</v>
       </c>
       <c r="P6" t="n">
         <v>164.818235627783</v>
@@ -8441,13 +8441,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>33.46371356783919</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>368.8098188445498</v>
+        <v>355.7883035217143</v>
       </c>
       <c r="N8" t="n">
         <v>285.7254304316443</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>56.91114161391758</v>
+        <v>103.3963705045923</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8517,7 +8517,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J9" t="n">
-        <v>217.9972017278486</v>
+        <v>206.9467504869447</v>
       </c>
       <c r="K9" t="n">
         <v>12.03922584486371</v>
@@ -8526,16 +8526,16 @@
         <v>159.3014045073375</v>
       </c>
       <c r="M9" t="n">
-        <v>402.3610913969162</v>
+        <v>409.2297782656032</v>
       </c>
       <c r="N9" t="n">
-        <v>201.4156280060917</v>
+        <v>371.4156280060917</v>
       </c>
       <c r="O9" t="n">
         <v>4.583748596270539</v>
       </c>
       <c r="P9" t="n">
-        <v>165.818235627783</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>17.27519534353338</v>
@@ -8678,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>35.46371356783919</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>355.7883035217143</v>
       </c>
       <c r="N11" t="n">
-        <v>285.7254304316443</v>
+        <v>304.6661376736718</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>111.3155624237843</v>
+        <v>56.91114161391758</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8760,7 +8760,7 @@
         <v>12.03922584486371</v>
       </c>
       <c r="L12" t="n">
-        <v>161.3014045073375</v>
+        <v>154.3519095578426</v>
       </c>
       <c r="M12" t="n">
         <v>411.2297782656032</v>
@@ -8772,7 +8772,7 @@
         <v>4.583748596270539</v>
       </c>
       <c r="P12" t="n">
-        <v>160.8687406782881</v>
+        <v>167.818235627783</v>
       </c>
       <c r="Q12" t="n">
         <v>17.27519534353338</v>
@@ -8915,16 +8915,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>35.46371356783919</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1.005139663657701</v>
+        <v>2.614663316582892</v>
       </c>
       <c r="M14" t="n">
         <v>355.7883035217143</v>
       </c>
       <c r="N14" t="n">
-        <v>285.7254304316443</v>
+        <v>319.5796203465583</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8994,22 +8994,22 @@
         <v>219.9972017278486</v>
       </c>
       <c r="K15" t="n">
-        <v>12.03922584486371</v>
+        <v>166.3911354027063</v>
       </c>
       <c r="L15" t="n">
-        <v>161.3014045073375</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>411.2297782656032</v>
       </c>
       <c r="N15" t="n">
-        <v>362.2843686843797</v>
+        <v>201.4156280060917</v>
       </c>
       <c r="O15" t="n">
         <v>4.583748596270539</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>167.818235627783</v>
       </c>
       <c r="Q15" t="n">
         <v>17.27519534353338</v>
@@ -9231,22 +9231,22 @@
         <v>219.9972017278486</v>
       </c>
       <c r="K18" t="n">
-        <v>184.0392258448637</v>
+        <v>12.03922584486371</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>239.2297782656032</v>
+        <v>411.2297782656032</v>
       </c>
       <c r="N18" t="n">
-        <v>355.7675375639343</v>
+        <v>373.4156280060917</v>
       </c>
       <c r="O18" t="n">
         <v>4.583748596270539</v>
       </c>
       <c r="P18" t="n">
-        <v>167.818235627783</v>
+        <v>150.1701451856256</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>117.7579561634021</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>51.46371356783922</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>18.61466331658289</v>
       </c>
       <c r="M20" t="n">
-        <v>355.7883035217143</v>
+        <v>369.5323152223244</v>
       </c>
       <c r="N20" t="n">
         <v>285.7254304316443</v>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>33.93556757836984</v>
       </c>
       <c r="Q20" t="n">
         <v>56.91114161391758</v>
@@ -9468,13 +9468,13 @@
         <v>47.99720172784856</v>
       </c>
       <c r="K21" t="n">
-        <v>200.0392258448637</v>
+        <v>12.03922584486371</v>
       </c>
       <c r="L21" t="n">
-        <v>169.7054449113779</v>
+        <v>177.3014045073375</v>
       </c>
       <c r="M21" t="n">
-        <v>239.2297782656032</v>
+        <v>427.2297782656032</v>
       </c>
       <c r="N21" t="n">
         <v>389.4156280060917</v>
@@ -9483,7 +9483,7 @@
         <v>4.583748596270539</v>
       </c>
       <c r="P21" t="n">
-        <v>183.818235627783</v>
+        <v>176.2222760318235</v>
       </c>
       <c r="Q21" t="n">
         <v>17.27519534353338</v>
@@ -9629,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>22.26019506624039</v>
+        <v>99.59339603779813</v>
       </c>
       <c r="M23" t="n">
         <v>355.7883035217143</v>
@@ -9638,13 +9638,13 @@
         <v>285.7254304316443</v>
       </c>
       <c r="O23" t="n">
-        <v>231.3976333931879</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>187.9355675783698</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>56.91114161391758</v>
+        <v>398.9111416139176</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>117.7579561634021</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>174.6690977773197</v>
+        <v>56.91114161391758</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,22 +9939,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>47.99720172784856</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
-        <v>12.03922584486371</v>
+        <v>200.0392258448637</v>
       </c>
       <c r="L27" t="n">
-        <v>169.7054449113779</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>239.2297782656032</v>
+        <v>417.4676829770412</v>
       </c>
       <c r="N27" t="n">
-        <v>389.4156280060917</v>
+        <v>201.4156280060917</v>
       </c>
       <c r="O27" t="n">
-        <v>192.5837485962705</v>
+        <v>4.583748596270539</v>
       </c>
       <c r="P27" t="n">
         <v>183.818235627783</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>58.36401676946265</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>56.91114161391758</v>
+        <v>115.2751583833802</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10179,22 +10179,22 @@
         <v>220.9972017278486</v>
       </c>
       <c r="K30" t="n">
-        <v>12.03922584486371</v>
+        <v>185.0392258448637</v>
       </c>
       <c r="L30" t="n">
-        <v>162.3014045073375</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>239.2297782656032</v>
       </c>
       <c r="N30" t="n">
-        <v>374.4156280060917</v>
+        <v>201.4156280060917</v>
       </c>
       <c r="O30" t="n">
-        <v>166.4120852341546</v>
+        <v>159.8952541137091</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>168.818235627783</v>
       </c>
       <c r="Q30" t="n">
         <v>17.27519534353338</v>
@@ -10340,10 +10340,10 @@
         <v>35.46371356783919</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.005139663657701</v>
       </c>
       <c r="M32" t="n">
-        <v>374.7290107637418</v>
+        <v>355.7883035217143</v>
       </c>
       <c r="N32" t="n">
         <v>285.7254304316443</v>
@@ -10352,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>17.93556757836984</v>
       </c>
       <c r="Q32" t="n">
         <v>56.91114161391758</v>
@@ -10419,19 +10419,19 @@
         <v>12.03922584486371</v>
       </c>
       <c r="L33" t="n">
-        <v>154.3519095578426</v>
+        <v>161.3014045073375</v>
       </c>
       <c r="M33" t="n">
-        <v>239.2297782656032</v>
+        <v>411.2297782656032</v>
       </c>
       <c r="N33" t="n">
         <v>373.4156280060917</v>
       </c>
       <c r="O33" t="n">
-        <v>176.5837485962705</v>
+        <v>165.4524892745586</v>
       </c>
       <c r="P33" t="n">
-        <v>167.818235627783</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10574,13 +10574,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>33.46371356783919</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>368.8098188445498</v>
+        <v>355.7883035217143</v>
       </c>
       <c r="N35" t="n">
         <v>285.7254304316443</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>56.91114161391758</v>
+        <v>103.3963705045923</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10650,7 +10650,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J36" t="n">
-        <v>47.99720172784856</v>
+        <v>217.9972017278486</v>
       </c>
       <c r="K36" t="n">
         <v>182.0392258448637</v>
@@ -10659,16 +10659,16 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>239.2297782656032</v>
+        <v>409.2297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>353.8483456447423</v>
+        <v>349.6665812725254</v>
       </c>
       <c r="O36" t="n">
-        <v>174.5837485962705</v>
+        <v>4.583748596270539</v>
       </c>
       <c r="P36" t="n">
-        <v>165.818235627783</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>46.48522889067472</v>
       </c>
       <c r="K38" t="n">
-        <v>33.46371356783919</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>69.93265693675306</v>
+        <v>56.91114161391758</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,13 +10887,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>47.99720172784856</v>
+        <v>217.9972017278486</v>
       </c>
       <c r="K39" t="n">
         <v>182.0392258448637</v>
       </c>
       <c r="L39" t="n">
-        <v>159.3014045073375</v>
+        <v>152.4327176386506</v>
       </c>
       <c r="M39" t="n">
         <v>239.2297782656032</v>
@@ -10902,7 +10902,7 @@
         <v>201.4156280060917</v>
       </c>
       <c r="O39" t="n">
-        <v>167.7150617275836</v>
+        <v>4.583748596270539</v>
       </c>
       <c r="P39" t="n">
         <v>165.818235627783</v>
@@ -11124,10 +11124,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>47.99720172784856</v>
+        <v>217.9972017278486</v>
       </c>
       <c r="K42" t="n">
-        <v>182.0392258448637</v>
+        <v>12.03922584486371</v>
       </c>
       <c r="L42" t="n">
         <v>159.3014045073375</v>
@@ -11364,7 +11364,7 @@
         <v>47.99720172784856</v>
       </c>
       <c r="K45" t="n">
-        <v>159.8170036226414</v>
+        <v>166.0392258448637</v>
       </c>
       <c r="L45" t="n">
         <v>143.3014045073375</v>
@@ -11376,7 +11376,7 @@
         <v>201.4156280060917</v>
       </c>
       <c r="O45" t="n">
-        <v>158.5837485962705</v>
+        <v>152.3615263740483</v>
       </c>
       <c r="P45" t="n">
         <v>149.818235627783</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>60.3575510912263</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -22524,7 +22524,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -22569,7 +22569,7 @@
         <v>181.9769184119809</v>
       </c>
       <c r="U2" t="n">
-        <v>121.0658613627343</v>
+        <v>249.135427201877</v>
       </c>
       <c r="V2" t="n">
         <v>75.85102416682389</v>
@@ -22581,7 +22581,7 @@
         <v>38.28183346066771</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>45.15815238615647</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22712,10 +22712,10 @@
         <v>18.39120342327726</v>
       </c>
       <c r="P4" t="n">
-        <v>229.2156350331956</v>
+        <v>191.0786414524215</v>
       </c>
       <c r="Q4" t="n">
-        <v>138.5434252309803</v>
+        <v>131.522266425598</v>
       </c>
       <c r="R4" t="n">
         <v>150.9532427352494</v>
@@ -22752,10 +22752,10 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -22806,7 +22806,7 @@
         <v>181.9769184119809</v>
       </c>
       <c r="U5" t="n">
-        <v>113.3033883945744</v>
+        <v>80.13542720187621</v>
       </c>
       <c r="V5" t="n">
         <v>60.85102416682315</v>
@@ -22815,7 +22815,7 @@
         <v>69.37347598094681</v>
       </c>
       <c r="X5" t="n">
-        <v>23.28183346066692</v>
+        <v>95.5852171565093</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -22949,13 +22949,13 @@
         <v>3.391203423277261</v>
       </c>
       <c r="P7" t="n">
-        <v>223.0247938385779</v>
+        <v>60.21563503319555</v>
       </c>
       <c r="Q7" t="n">
         <v>116.522266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>135.9532427352494</v>
+        <v>298.7624015406319</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,22 +22986,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>2.684005452845383</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -23040,19 +23040,19 @@
         <v>70.38882106865458</v>
       </c>
       <c r="T8" t="n">
-        <v>181.9769184119809</v>
+        <v>11.97691841198099</v>
       </c>
       <c r="U8" t="n">
-        <v>79.13542720187701</v>
+        <v>102.0834326547224</v>
       </c>
       <c r="V8" t="n">
         <v>59.85102416682389</v>
       </c>
       <c r="W8" t="n">
-        <v>185.3392342832405</v>
+        <v>68.37347598094755</v>
       </c>
       <c r="X8" t="n">
-        <v>22.28183346066771</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -23226,10 +23226,10 @@
         <v>208.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>176.4745782429939</v>
+        <v>4.474578242993914</v>
       </c>
       <c r="D11" t="n">
-        <v>137.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>131.3632896068686</v>
@@ -23238,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>129.6840054528454</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>124.0170406130752</v>
@@ -23277,22 +23277,22 @@
         <v>197.3888210686546</v>
       </c>
       <c r="T11" t="n">
-        <v>136.976918411981</v>
+        <v>308.976918411981</v>
       </c>
       <c r="U11" t="n">
-        <v>356.527455909889</v>
+        <v>376.135427201877</v>
       </c>
       <c r="V11" t="n">
-        <v>184.8510241668239</v>
+        <v>356.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>365.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>147.2818334606677</v>
+        <v>319.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>238.3174326828064</v>
+        <v>141.7326225835134</v>
       </c>
     </row>
     <row r="12">
@@ -23302,25 +23302,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>111.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>88.09991244551929</v>
       </c>
       <c r="D12" t="n">
         <v>74.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>69.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>66.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>52.16523398823489</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.326392486682363</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23356,10 +23356,10 @@
         <v>182.896594304234</v>
       </c>
       <c r="T12" t="n">
-        <v>130.0429255948723</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>127.1725767413188</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -23371,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>126.3913927661343</v>
+        <v>52.76899622467177</v>
       </c>
     </row>
     <row r="13">
@@ -23411,28 +23411,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>78.9653658626972</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1581523861456162</v>
+        <v>20.6605523861369</v>
       </c>
       <c r="N13" t="n">
-        <v>224.5062064192259</v>
+        <v>52.50620641922586</v>
       </c>
       <c r="O13" t="n">
-        <v>135.8416457101328</v>
+        <v>127.3912034232772</v>
       </c>
       <c r="P13" t="n">
-        <v>356.2156350331956</v>
+        <v>184.2156350331955</v>
       </c>
       <c r="Q13" t="n">
-        <v>240.522266425598</v>
+        <v>412.522266425598</v>
       </c>
       <c r="R13" t="n">
         <v>431.9532427352494</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>80.98267642416691</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23466,19 +23466,19 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>59.33915573984979</v>
       </c>
       <c r="E14" t="n">
         <v>53.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>53.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>51.68400545284538</v>
       </c>
       <c r="H14" t="n">
-        <v>46.01704061307515</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,25 +23511,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>119.3888210686546</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>230.9769184119809</v>
       </c>
       <c r="U14" t="n">
-        <v>126.135427201877</v>
+        <v>280.725328517419</v>
       </c>
       <c r="V14" t="n">
-        <v>113.1671581496677</v>
+        <v>278.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>115.3734759809475</v>
+        <v>287.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>241.2818334606677</v>
+        <v>69.28183346066771</v>
       </c>
       <c r="Y14" t="n">
-        <v>160.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23587,10 +23587,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5.025610997898184</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>5.025610997898198</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
@@ -23651,22 +23651,22 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>94.15815238615647</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>146.5062064192259</v>
       </c>
       <c r="O16" t="n">
         <v>49.39120342327726</v>
       </c>
       <c r="P16" t="n">
-        <v>199.330436125442</v>
+        <v>106.2156350331956</v>
       </c>
       <c r="Q16" t="n">
-        <v>162.522266425598</v>
+        <v>186.9727087124622</v>
       </c>
       <c r="R16" t="n">
-        <v>353.9532427352494</v>
+        <v>181.9532427352494</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -23715,7 +23715,7 @@
         <v>51.68400545284535</v>
       </c>
       <c r="H17" t="n">
-        <v>46.01704061307515</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>13.90826168172983</v>
       </c>
       <c r="T17" t="n">
         <v>230.976918411981</v>
@@ -23757,16 +23757,16 @@
         <v>126.135427201877</v>
       </c>
       <c r="V17" t="n">
-        <v>278.8510241668239</v>
+        <v>106.8510241668239</v>
       </c>
       <c r="W17" t="n">
         <v>115.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>197.4904872121287</v>
+        <v>241.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>160.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -23885,10 +23885,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.9653658626971975</v>
       </c>
       <c r="M19" t="n">
-        <v>94.15815238615646</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -23897,16 +23897,16 @@
         <v>49.39120342327723</v>
       </c>
       <c r="P19" t="n">
-        <v>106.2156350331955</v>
+        <v>278.2156350331956</v>
       </c>
       <c r="Q19" t="n">
-        <v>333.478915131688</v>
+        <v>251.6890252309804</v>
       </c>
       <c r="R19" t="n">
         <v>181.9532427352494</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.982676424166913</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>130.9993129555745</v>
+        <v>96.44583159817461</v>
       </c>
       <c r="C20" t="n">
         <v>98.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>59.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>53.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>51.68400545284538</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -23985,16 +23985,16 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>119.3888210686546</v>
       </c>
       <c r="T20" t="n">
-        <v>230.9769184119809</v>
+        <v>42.97691841198099</v>
       </c>
       <c r="U20" t="n">
-        <v>110.135427201877</v>
+        <v>298.135427201877</v>
       </c>
       <c r="V20" t="n">
-        <v>249.6034096162796</v>
+        <v>278.8510241668239</v>
       </c>
       <c r="W20" t="n">
         <v>287.3734759809475</v>
@@ -24003,7 +24003,7 @@
         <v>53.28183346066771</v>
       </c>
       <c r="Y20" t="n">
-        <v>160.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24125,7 +24125,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>94.15815238615647</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24134,16 +24134,16 @@
         <v>33.39120342327726</v>
       </c>
       <c r="P22" t="n">
-        <v>90.21563503319555</v>
+        <v>263.0794837392856</v>
       </c>
       <c r="Q22" t="n">
-        <v>222.5615910936776</v>
+        <v>146.522266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>353.9532427352494</v>
+        <v>165.9532427352494</v>
       </c>
       <c r="S22" t="n">
-        <v>2.982676424166925</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>130.9993129555745</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -24180,13 +24180,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>53.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>53.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>51.68400545284538</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>46.01704061307515</v>
@@ -24222,22 +24222,22 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>11.67987976440477</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>77.18668128271253</v>
       </c>
       <c r="V23" t="n">
-        <v>278.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>287.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.2818334606677</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -24408,13 +24408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>205.9993129555745</v>
+        <v>17.99931295557451</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>134.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>128.3632896068686</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>126.6840054528454</v>
+        <v>8.474853016926334</v>
       </c>
       <c r="H26" t="n">
-        <v>121.0170406130752</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24471,10 +24471,10 @@
         <v>353.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>174.3734759809475</v>
+        <v>362.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>211.3947961515233</v>
+        <v>316.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>235.3174326828064</v>
@@ -24487,7 +24487,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>108.5565566463266</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -24499,7 +24499,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>52.38673224831139</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>49.16523398823489</v>
@@ -24541,10 +24541,10 @@
         <v>179.896594304234</v>
       </c>
       <c r="T27" t="n">
-        <v>127.0429255948723</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>91.34444787611027</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -24553,10 +24553,10 @@
         <v>156.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>143.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>123.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -24611,13 +24611,13 @@
         <v>353.2156350331956</v>
       </c>
       <c r="Q28" t="n">
-        <v>302.0716535642184</v>
+        <v>409.522266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>428.9532427352494</v>
+        <v>399.4853062980368</v>
       </c>
       <c r="S28" t="n">
-        <v>77.98267642416691</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24648,22 +24648,22 @@
         <v>129.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>97.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>58.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>52.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>52.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>50.68400545284535</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>45.01704061307515</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,19 +24699,19 @@
         <v>118.3888210686546</v>
       </c>
       <c r="T29" t="n">
-        <v>77.59851841198112</v>
+        <v>209.0029271687571</v>
       </c>
       <c r="U29" t="n">
-        <v>297.135427201877</v>
+        <v>124.135427201877</v>
       </c>
       <c r="V29" t="n">
         <v>104.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>113.3734759809475</v>
+        <v>286.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>67.28183346066771</v>
+        <v>240.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>159.3174326828064</v>
@@ -24842,16 +24842,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>47.39120342327723</v>
+        <v>220.3912034232772</v>
       </c>
       <c r="P31" t="n">
-        <v>104.2156350331955</v>
+        <v>192.4842702627448</v>
       </c>
       <c r="Q31" t="n">
-        <v>248.7909016551473</v>
+        <v>160.522266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>352.9532427352494</v>
+        <v>179.9532427352494</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -24882,13 +24882,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>78.99931295557451</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>7.339155739849787</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -24936,19 +24936,19 @@
         <v>67.38882106865458</v>
       </c>
       <c r="T32" t="n">
-        <v>6.976918411980989</v>
+        <v>13.52424765266184</v>
       </c>
       <c r="U32" t="n">
         <v>246.135427201877</v>
       </c>
       <c r="V32" t="n">
-        <v>226.8510241668239</v>
+        <v>54.85102416682389</v>
       </c>
       <c r="W32" t="n">
-        <v>156.2592739170527</v>
+        <v>63.37347598094755</v>
       </c>
       <c r="X32" t="n">
-        <v>17.28183346066771</v>
+        <v>189.2818334606677</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -25122,10 +25122,10 @@
         <v>78.99931295557451</v>
       </c>
       <c r="C35" t="n">
-        <v>46.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>7.339155739849787</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -25173,7 +25173,7 @@
         <v>67.38882106865458</v>
       </c>
       <c r="T35" t="n">
-        <v>39.83299246671129</v>
+        <v>78.96841496985537</v>
       </c>
       <c r="U35" t="n">
         <v>76.13542720187701</v>
@@ -25182,10 +25182,10 @@
         <v>56.85102416682389</v>
       </c>
       <c r="W35" t="n">
-        <v>65.37347598094755</v>
+        <v>235.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>189.2818334606677</v>
+        <v>19.28183346066771</v>
       </c>
       <c r="Y35" t="n">
         <v>108.3174326828064</v>
@@ -25310,7 +25310,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>42.15815238615647</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -25319,10 +25319,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>212.5351972618551</v>
+        <v>56.21563503319555</v>
       </c>
       <c r="Q37" t="n">
-        <v>112.522266425598</v>
+        <v>226.6836762681011</v>
       </c>
       <c r="R37" t="n">
         <v>131.9532427352494</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25407,22 +25407,22 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>67.38882106865458</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>178.9769184119809</v>
+        <v>8.976918411980989</v>
       </c>
       <c r="U38" t="n">
-        <v>91.78351218240758</v>
+        <v>76.13542720187701</v>
       </c>
       <c r="V38" t="n">
-        <v>56.85102416682389</v>
+        <v>226.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>65.37347598094755</v>
+        <v>235.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>189.2818334606677</v>
+        <v>181.3180524654274</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -25547,19 +25547,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>42.15815238615647</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>156.3195622286595</v>
       </c>
       <c r="P40" t="n">
         <v>56.21563503319555</v>
       </c>
       <c r="Q40" t="n">
-        <v>226.6836762681011</v>
+        <v>112.522266425598</v>
       </c>
       <c r="R40" t="n">
         <v>131.9532427352494</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>105.9993129555745</v>
+        <v>275.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>73.47457824299391</v>
+        <v>243.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>34.33915573984979</v>
+        <v>204.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>198.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>198.8896287080119</v>
+        <v>28.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>196.6840054528454</v>
+        <v>26.68400545284535</v>
       </c>
       <c r="H41" t="n">
         <v>191.0170406130752</v>
@@ -25644,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>264.3888210686546</v>
+        <v>94.38882106865458</v>
       </c>
       <c r="T41" t="n">
-        <v>375.9769184119809</v>
+        <v>226.240918411981</v>
       </c>
       <c r="U41" t="n">
         <v>443.135427201877</v>
@@ -25662,7 +25662,7 @@
         <v>386.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>155.5814326828064</v>
+        <v>305.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25675,22 +25675,22 @@
         <v>178.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>155.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>141.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>136.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>133.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>119.1652339882349</v>
+        <v>41.82278367227663</v>
       </c>
       <c r="H42" t="n">
-        <v>120.6215400166098</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,22 +25720,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>135.6167029527567</v>
+        <v>305.6167029527567</v>
       </c>
       <c r="S42" t="n">
-        <v>100.1605943042339</v>
+        <v>249.8965943042339</v>
       </c>
       <c r="T42" t="n">
         <v>197.0429255948723</v>
       </c>
       <c r="U42" t="n">
-        <v>194.1725767413188</v>
+        <v>24.17257674131884</v>
       </c>
       <c r="V42" t="n">
-        <v>38.51066719152016</v>
+        <v>208.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>56.37314290982852</v>
+        <v>226.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>213.8627394453875</v>
@@ -25769,7 +25769,7 @@
         <v>38.56239743169397</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>18.49037200325796</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25778,16 +25778,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>26.5820852765529</v>
       </c>
       <c r="L43" t="n">
         <v>145.9653658626972</v>
       </c>
       <c r="M43" t="n">
-        <v>239.1581523861565</v>
+        <v>69.15815238615647</v>
       </c>
       <c r="N43" t="n">
-        <v>291.5062064192259</v>
+        <v>213.590279115694</v>
       </c>
       <c r="O43" t="n">
         <v>366.3912034232773</v>
@@ -25802,7 +25802,7 @@
         <v>498.9532427352494</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>147.9826764241669</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>41.44364543010755</v>
       </c>
       <c r="Y43" t="n">
-        <v>68.04820468001586</v>
+        <v>81.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -25833,13 +25833,13 @@
         <v>429.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>243.4745782429939</v>
+        <v>397.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>279.3961405481625</v>
+        <v>204.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>198.3632896068686</v>
+        <v>352.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>352.8896287080119</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>131.4537194313095</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>418.3888210686546</v>
@@ -25887,16 +25887,16 @@
         <v>529.9769184119809</v>
       </c>
       <c r="U44" t="n">
-        <v>443.135427201877</v>
+        <v>597.135427201877</v>
       </c>
       <c r="V44" t="n">
-        <v>577.8510241668239</v>
+        <v>423.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>586.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>540.2818334606677</v>
+        <v>438.79253770029</v>
       </c>
       <c r="Y44" t="n">
         <v>459.3174326828064</v>
@@ -25912,7 +25912,7 @@
         <v>332.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>155.0999124455193</v>
+        <v>309.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>295.9376868977026</v>
@@ -25921,7 +25921,7 @@
         <v>290.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>143.3463150216782</v>
+        <v>287.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>273.1652339882349</v>
@@ -25930,7 +25930,7 @@
         <v>274.6215400166098</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>57.4802056988092</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,13 +25954,13 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>47.77013301500788</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>459.6167029527567</v>
+        <v>305.6167029527567</v>
       </c>
       <c r="S45" t="n">
-        <v>403.8965943042339</v>
+        <v>249.896594304234</v>
       </c>
       <c r="T45" t="n">
         <v>351.0429255948723</v>
@@ -25972,10 +25972,10 @@
         <v>362.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>380.3731429098285</v>
+        <v>226.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>213.8627394453875</v>
+        <v>367.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>347.3913927661343</v>
@@ -26045,10 +26045,10 @@
         <v>155.9673533915036</v>
       </c>
       <c r="U46" t="n">
-        <v>49.17111645640001</v>
+        <v>98.93212897937597</v>
       </c>
       <c r="V46" t="n">
-        <v>147.1703102162162</v>
+        <v>97.40929769324023</v>
       </c>
       <c r="W46" t="n">
         <v>174.3728098387097</v>
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2077824.187851256</v>
+        <v>2077824.187851257</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3918246.670159646</v>
+        <v>3918246.670159645</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4875320.076253451</v>
+        <v>4875320.07625345</v>
       </c>
     </row>
     <row r="7">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8657505.022354273</v>
+        <v>8657505.022354271</v>
       </c>
     </row>
     <row r="11">
@@ -26269,16 +26269,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1062417.413308976</v>
+        <v>1062417.413308977</v>
       </c>
       <c r="C2" t="n">
-        <v>1067845.100188976</v>
+        <v>1067845.100188977</v>
       </c>
       <c r="D2" t="n">
         <v>1068206.945980977</v>
       </c>
       <c r="E2" t="n">
-        <v>879799.7900807374</v>
+        <v>879799.7900807377</v>
       </c>
       <c r="F2" t="n">
         <v>1013371.84174638</v>
@@ -26308,10 +26308,10 @@
         <v>1071367.068131619</v>
       </c>
       <c r="O2" t="n">
-        <v>740288.5720876259</v>
+        <v>740288.5720876257</v>
       </c>
       <c r="P2" t="n">
-        <v>391030.571193053</v>
+        <v>391030.5711930529</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>568980.5380828825</v>
+        <v>568974.0684166315</v>
       </c>
       <c r="C4" t="n">
-        <v>569162.2824260858</v>
+        <v>569155.5342610902</v>
       </c>
       <c r="D4" t="n">
-        <v>567309.8932225504</v>
+        <v>567303.1242140777</v>
       </c>
       <c r="E4" t="n">
-        <v>446720.6797691238</v>
+        <v>446713.8662473008</v>
       </c>
       <c r="F4" t="n">
-        <v>528826.3644095176</v>
+        <v>528819.5508876945</v>
       </c>
       <c r="G4" t="n">
-        <v>526938.8929398406</v>
+        <v>526932.0794180174</v>
       </c>
       <c r="H4" t="n">
-        <v>528122.0995188614</v>
+        <v>528114.9298902352</v>
       </c>
       <c r="I4" t="n">
-        <v>554690.0639907896</v>
+        <v>554679.4668341838</v>
       </c>
       <c r="J4" t="n">
-        <v>446618.8264415116</v>
+        <v>446611.6568128854</v>
       </c>
       <c r="K4" t="n">
-        <v>520386.2450870424</v>
+        <v>520379.4093085441</v>
       </c>
       <c r="L4" t="n">
-        <v>553333.2998195969</v>
+        <v>553326.4862977739</v>
       </c>
       <c r="M4" t="n">
-        <v>550906.9170275889</v>
+        <v>550900.1480191163</v>
       </c>
       <c r="N4" t="n">
-        <v>548848.1397406175</v>
+        <v>548841.3707321447</v>
       </c>
       <c r="O4" t="n">
-        <v>346988.0223316727</v>
+        <v>346981.2533232</v>
       </c>
       <c r="P4" t="n">
-        <v>137069.5148939267</v>
+        <v>137063.0452276758</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>130092.4752260939</v>
+        <v>130098.9448923451</v>
       </c>
       <c r="C6" t="n">
-        <v>443679.4177628906</v>
+        <v>443686.1659278864</v>
       </c>
       <c r="D6" t="n">
-        <v>450760.8527584262</v>
+        <v>450767.6217668991</v>
       </c>
       <c r="E6" t="n">
-        <v>174746.0733116136</v>
+        <v>174752.8868334369</v>
       </c>
       <c r="F6" t="n">
-        <v>376359.0583368621</v>
+        <v>376365.8718586853</v>
       </c>
       <c r="G6" t="n">
-        <v>440646.5298065392</v>
+        <v>440653.3433283623</v>
       </c>
       <c r="H6" t="n">
-        <v>438839.8332151983</v>
+        <v>438847.0028438245</v>
       </c>
       <c r="I6" t="n">
-        <v>410056.92071127</v>
+        <v>410067.517867876</v>
       </c>
       <c r="J6" t="n">
-        <v>247708.4421512064</v>
+        <v>247715.6117798326</v>
       </c>
       <c r="K6" t="n">
-        <v>325582.943669652</v>
+        <v>325589.7794481502</v>
       </c>
       <c r="L6" t="n">
-        <v>427799.4528960219</v>
+        <v>427806.2664178449</v>
       </c>
       <c r="M6" t="n">
-        <v>470423.74410403</v>
+        <v>470430.5131125026</v>
       </c>
       <c r="N6" t="n">
-        <v>472482.5213910014</v>
+        <v>472489.2903994742</v>
       </c>
       <c r="O6" t="n">
-        <v>359025.7357559532</v>
+        <v>359032.5047644257</v>
       </c>
       <c r="P6" t="n">
-        <v>234405.6682991263</v>
+        <v>234412.137965377</v>
       </c>
     </row>
   </sheetData>
@@ -27557,16 +27557,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>44.55935656005349</v>
       </c>
       <c r="R3" t="n">
-        <v>391.7056878506919</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>301.8965943042339</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>400</v>
+        <v>249.0429255948723</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,13 +27591,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>301.4872717550073</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
@@ -27609,7 +27609,7 @@
         <v>244.562397431694</v>
       </c>
       <c r="H4" t="n">
-        <v>224.490372003258</v>
+        <v>378.490372003258</v>
       </c>
       <c r="I4" t="n">
         <v>162.1541769315937</v>
@@ -27645,22 +27645,22 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>361.9673533915036</v>
+        <v>207.9673533915036</v>
       </c>
       <c r="U4" t="n">
-        <v>150.932128979376</v>
+        <v>304.932128979376</v>
       </c>
       <c r="V4" t="n">
-        <v>353.1703102162162</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>390.3178999691308</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27749,19 +27749,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>215.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>192.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>267.5578360376206</v>
       </c>
       <c r="E6" t="n">
-        <v>193.0623793768385</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>170.6362423378769</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.1652339882349</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>99.77013301500787</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>162.1541769315937</v>
       </c>
       <c r="J7" t="n">
-        <v>1.228637360497942</v>
+        <v>170.2286373604979</v>
       </c>
       <c r="K7" t="n">
         <v>232.5820852765529</v>
@@ -27885,7 +27885,7 @@
         <v>207.9673533915036</v>
       </c>
       <c r="U7" t="n">
-        <v>217.0128444306631</v>
+        <v>150.932128979376</v>
       </c>
       <c r="V7" t="n">
         <v>368.1703102162162</v>
@@ -27897,7 +27897,7 @@
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>297.0807154512871</v>
       </c>
     </row>
     <row r="8">
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>99.77013301500787</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>341.6167029527567</v>
       </c>
       <c r="S9" t="n">
-        <v>285.8965943042339</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>320.2260518829274</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>305.8927792021692</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28074,10 +28074,10 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28086,16 +28086,16 @@
         <v>394.490372003258</v>
       </c>
       <c r="I10" t="n">
-        <v>265.2116482992992</v>
+        <v>294.3953386338509</v>
       </c>
       <c r="J10" t="n">
         <v>1.228637360497942</v>
       </c>
       <c r="K10" t="n">
-        <v>232.5820852765529</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>351.9653658626972</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28539,34 +28539,34 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C16" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D16" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E16" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F16" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G16" t="n">
         <v>351</v>
       </c>
-      <c r="C16" t="n">
+      <c r="H16" t="n">
         <v>351</v>
       </c>
-      <c r="D16" t="n">
-        <v>351</v>
-      </c>
-      <c r="E16" t="n">
-        <v>351</v>
-      </c>
-      <c r="F16" t="n">
-        <v>351</v>
-      </c>
-      <c r="G16" t="n">
-        <v>244.562397431694</v>
-      </c>
-      <c r="H16" t="n">
-        <v>224.490372003258</v>
-      </c>
       <c r="I16" t="n">
-        <v>162.1541769315937</v>
+        <v>334.1541769315937</v>
       </c>
       <c r="J16" t="n">
         <v>1.228637360497942</v>
       </c>
       <c r="K16" t="n">
-        <v>232.5820852765529</v>
+        <v>351</v>
       </c>
       <c r="L16" t="n">
         <v>351</v>
@@ -28593,22 +28593,22 @@
         <v>351</v>
       </c>
       <c r="T16" t="n">
+        <v>207.9673533915036</v>
+      </c>
+      <c r="U16" t="n">
+        <v>156.787798957602</v>
+      </c>
+      <c r="V16" t="n">
         <v>351</v>
-      </c>
-      <c r="U16" t="n">
-        <v>150.932128979376</v>
-      </c>
-      <c r="V16" t="n">
-        <v>215.8361927831721</v>
       </c>
       <c r="W16" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X16" t="n">
-        <v>351</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y16" t="n">
-        <v>351</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="17">
@@ -28776,25 +28776,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>287.1138003370787</v>
+        <v>351</v>
       </c>
       <c r="C19" t="n">
-        <v>272.7252466480447</v>
+        <v>308.2347980144028</v>
       </c>
       <c r="D19" t="n">
-        <v>285.5362180555555</v>
+        <v>351</v>
       </c>
       <c r="E19" t="n">
-        <v>280.9809048369565</v>
+        <v>351</v>
       </c>
       <c r="F19" t="n">
-        <v>274.3828559677419</v>
+        <v>351</v>
       </c>
       <c r="G19" t="n">
         <v>244.562397431694</v>
       </c>
       <c r="H19" t="n">
-        <v>224.490372003258</v>
+        <v>351</v>
       </c>
       <c r="I19" t="n">
         <v>162.1541769315937</v>
@@ -28830,13 +28830,13 @@
         <v>351</v>
       </c>
       <c r="T19" t="n">
-        <v>322.1430637734874</v>
+        <v>207.9673533915036</v>
       </c>
       <c r="U19" t="n">
-        <v>322.932128979376</v>
+        <v>150.932128979376</v>
       </c>
       <c r="V19" t="n">
-        <v>351</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W19" t="n">
         <v>351</v>
@@ -28943,13 +28943,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>285.6049082198109</v>
       </c>
       <c r="F21" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>268.0980449861331</v>
+        <v>325.1652339882349</v>
       </c>
       <c r="H21" t="n">
         <v>326.6215400166098</v>
@@ -29016,7 +29016,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C22" t="n">
-        <v>272.7252466480447</v>
+        <v>351</v>
       </c>
       <c r="D22" t="n">
         <v>285.5362180555555</v>
@@ -29031,16 +29031,16 @@
         <v>244.562397431694</v>
       </c>
       <c r="H22" t="n">
-        <v>351</v>
+        <v>224.490372003258</v>
       </c>
       <c r="I22" t="n">
-        <v>193.4680610648914</v>
+        <v>329.8523147452651</v>
       </c>
       <c r="J22" t="n">
         <v>1.228637360497942</v>
       </c>
       <c r="K22" t="n">
-        <v>232.5820852765529</v>
+        <v>351</v>
       </c>
       <c r="L22" t="n">
         <v>351</v>
@@ -29067,7 +29067,7 @@
         <v>351</v>
       </c>
       <c r="T22" t="n">
-        <v>351</v>
+        <v>207.9673533915036</v>
       </c>
       <c r="U22" t="n">
         <v>150.932128979376</v>
@@ -29082,7 +29082,7 @@
         <v>351</v>
       </c>
       <c r="Y22" t="n">
-        <v>351</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="23">
@@ -29171,16 +29171,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>42.55655664632661</v>
+        <v>351</v>
       </c>
       <c r="C24" t="n">
         <v>351</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>5.937686897702633</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>29.96170821981065</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29219,7 +29219,7 @@
         <v>99.77013301500787</v>
       </c>
       <c r="R24" t="n">
-        <v>298.3416615854374</v>
+        <v>351</v>
       </c>
       <c r="S24" t="n">
         <v>351</v>
@@ -29240,7 +29240,7 @@
         <v>351</v>
       </c>
       <c r="Y24" t="n">
-        <v>57.39139276613435</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25">
@@ -29250,13 +29250,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>287.1138003370787</v>
+        <v>351</v>
       </c>
       <c r="C25" t="n">
-        <v>351</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
-        <v>351</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E25" t="n">
         <v>351</v>
@@ -29268,7 +29268,7 @@
         <v>351</v>
       </c>
       <c r="H25" t="n">
-        <v>237.7337389409352</v>
+        <v>224.490372003258</v>
       </c>
       <c r="I25" t="n">
         <v>351</v>
@@ -29304,22 +29304,22 @@
         <v>351</v>
       </c>
       <c r="T25" t="n">
+        <v>207.9673533915036</v>
+      </c>
+      <c r="U25" t="n">
+        <v>247.1719760610914</v>
+      </c>
+      <c r="V25" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W25" t="n">
         <v>351</v>
       </c>
-      <c r="U25" t="n">
-        <v>150.932128979376</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>351</v>
       </c>
-      <c r="W25" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X25" t="n">
-        <v>247.4436454301076</v>
-      </c>
       <c r="Y25" t="n">
-        <v>287.4653528494624</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26">
@@ -29663,10 +29663,10 @@
         <v>325.1652339882349</v>
       </c>
       <c r="H30" t="n">
-        <v>317.7663510145081</v>
+        <v>326.6215400166098</v>
       </c>
       <c r="I30" t="n">
-        <v>197.3532726838014</v>
+        <v>188.4980836816996</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29727,31 +29727,31 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C31" t="n">
-        <v>272.7252466480447</v>
+        <v>352</v>
       </c>
       <c r="D31" t="n">
-        <v>285.5362180555555</v>
+        <v>352</v>
       </c>
       <c r="E31" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F31" t="n">
-        <v>274.3828559677419</v>
+        <v>352</v>
       </c>
       <c r="G31" t="n">
         <v>244.562397431694</v>
       </c>
       <c r="H31" t="n">
-        <v>352</v>
+        <v>224.490372003258</v>
       </c>
       <c r="I31" t="n">
-        <v>322.6457465143103</v>
+        <v>335.1541769315937</v>
       </c>
       <c r="J31" t="n">
         <v>1.228637360497942</v>
       </c>
       <c r="K31" t="n">
-        <v>352</v>
+        <v>232.5820852765529</v>
       </c>
       <c r="L31" t="n">
         <v>352</v>
@@ -29781,16 +29781,16 @@
         <v>207.9673533915036</v>
       </c>
       <c r="U31" t="n">
-        <v>323.932128979376</v>
+        <v>313.924726362226</v>
       </c>
       <c r="V31" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W31" t="n">
-        <v>226.3728098387097</v>
+        <v>352</v>
       </c>
       <c r="X31" t="n">
-        <v>352</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y31" t="n">
         <v>287.4653528494624</v>
@@ -29903,7 +29903,7 @@
         <v>326.6215400166098</v>
       </c>
       <c r="I33" t="n">
-        <v>25.35327268380136</v>
+        <v>197.3532726838014</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,28 +29927,28 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>99.77013301500787</v>
       </c>
       <c r="R33" t="n">
-        <v>398.5323798187347</v>
+        <v>403</v>
       </c>
       <c r="S33" t="n">
         <v>403</v>
       </c>
       <c r="T33" t="n">
-        <v>231.0429255948723</v>
+        <v>403.0000000000039</v>
       </c>
       <c r="U33" t="n">
         <v>400.1725767413188</v>
       </c>
       <c r="V33" t="n">
-        <v>403</v>
+        <v>242.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>403</v>
+        <v>260.3731429098285</v>
       </c>
       <c r="X33" t="n">
-        <v>403</v>
+        <v>257.9213622972466</v>
       </c>
       <c r="Y33" t="n">
         <v>399.3913927661343</v>
@@ -29979,19 +29979,19 @@
         <v>244.562397431694</v>
       </c>
       <c r="H34" t="n">
-        <v>396.490372003258</v>
+        <v>224.490372003258</v>
       </c>
       <c r="I34" t="n">
-        <v>277.7521331213488</v>
+        <v>162.1541769315937</v>
       </c>
       <c r="J34" t="n">
-        <v>173.2286373604979</v>
+        <v>1.228637360497942</v>
       </c>
       <c r="K34" t="n">
-        <v>403</v>
+        <v>232.5820852765529</v>
       </c>
       <c r="L34" t="n">
-        <v>403</v>
+        <v>351.9653658626972</v>
       </c>
       <c r="M34" t="n">
         <v>403</v>
@@ -30015,22 +30015,22 @@
         <v>353.9826764241669</v>
       </c>
       <c r="T34" t="n">
-        <v>207.9673533915036</v>
+        <v>273.9268567215786</v>
       </c>
       <c r="U34" t="n">
-        <v>150.932128979376</v>
+        <v>322.932128979376</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>371.1703102162162</v>
       </c>
       <c r="W34" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X34" t="n">
-        <v>247.4436454301076</v>
+        <v>403</v>
       </c>
       <c r="Y34" t="n">
-        <v>287.4653528494624</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35">
@@ -30125,7 +30125,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>177.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30140,7 +30140,7 @@
         <v>326.6215400166098</v>
       </c>
       <c r="I36" t="n">
-        <v>85.40937789087712</v>
+        <v>197.3532726838014</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30170,16 +30170,16 @@
         <v>403</v>
       </c>
       <c r="S36" t="n">
+        <v>285.8965943042339</v>
+      </c>
+      <c r="T36" t="n">
+        <v>403.0000000000036</v>
+      </c>
+      <c r="U36" t="n">
+        <v>246.8427548356804</v>
+      </c>
+      <c r="V36" t="n">
         <v>403</v>
-      </c>
-      <c r="T36" t="n">
-        <v>403.0000000000032</v>
-      </c>
-      <c r="U36" t="n">
-        <v>230.1725767413188</v>
-      </c>
-      <c r="V36" t="n">
-        <v>244.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>403</v>
@@ -30213,13 +30213,13 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>403</v>
+        <v>244.562397431694</v>
       </c>
       <c r="H37" t="n">
-        <v>394.490372003258</v>
+        <v>353.0480069888455</v>
       </c>
       <c r="I37" t="n">
-        <v>332.1541769315937</v>
+        <v>162.1541769315937</v>
       </c>
       <c r="J37" t="n">
         <v>1.228637360497942</v>
@@ -30228,7 +30228,7 @@
         <v>232.5820852765529</v>
       </c>
       <c r="L37" t="n">
-        <v>403</v>
+        <v>351.9653658626972</v>
       </c>
       <c r="M37" t="n">
         <v>403</v>
@@ -30252,10 +30252,10 @@
         <v>403</v>
       </c>
       <c r="T37" t="n">
-        <v>282.6091062413748</v>
+        <v>377.9673533915036</v>
       </c>
       <c r="U37" t="n">
-        <v>150.932128979376</v>
+        <v>320.932128979376</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
@@ -30264,7 +30264,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>403</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30377,7 +30377,7 @@
         <v>156.6215400166098</v>
       </c>
       <c r="I39" t="n">
-        <v>96.92004508239751</v>
+        <v>96.87711948752826</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30410,7 +30410,7 @@
         <v>403</v>
       </c>
       <c r="T39" t="n">
-        <v>403.0000000000031</v>
+        <v>233.0429255948723</v>
       </c>
       <c r="U39" t="n">
         <v>400.1725767413188</v>
@@ -30425,7 +30425,7 @@
         <v>403</v>
       </c>
       <c r="Y39" t="n">
-        <v>229.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -30441,7 +30441,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>293.1111766169761</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30459,7 +30459,7 @@
         <v>162.1541769315937</v>
       </c>
       <c r="J40" t="n">
-        <v>1.228637360497942</v>
+        <v>171.2286373604979</v>
       </c>
       <c r="K40" t="n">
         <v>402.5820852765529</v>
@@ -30486,22 +30486,22 @@
         <v>403</v>
       </c>
       <c r="S40" t="n">
-        <v>353.9826764241669</v>
+        <v>403</v>
       </c>
       <c r="T40" t="n">
-        <v>207.9673533915036</v>
+        <v>377.9673533915036</v>
       </c>
       <c r="U40" t="n">
-        <v>150.932128979376</v>
+        <v>265.046118534856</v>
       </c>
       <c r="V40" t="n">
-        <v>369.1703102162162</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>396.3728098387097</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>403</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
         <v>287.4653528494624</v>
@@ -33713,7 +33713,7 @@
         <v>136.5362864321608</v>
       </c>
       <c r="L35" t="n">
-        <v>169.3853366834171</v>
+        <v>169.3853366834172</v>
       </c>
       <c r="M35" t="n">
         <v>188.473824120603</v>
@@ -33950,7 +33950,7 @@
         <v>136.5362864321608</v>
       </c>
       <c r="L38" t="n">
-        <v>169.3853366834173</v>
+        <v>169.3853366834172</v>
       </c>
       <c r="M38" t="n">
         <v>188.473824120603</v>
@@ -34187,7 +34187,7 @@
         <v>136.5362864321608</v>
       </c>
       <c r="L41" t="n">
-        <v>169.3853366834173</v>
+        <v>169.3853366834171</v>
       </c>
       <c r="M41" t="n">
         <v>188.473824120603</v>
@@ -34828,10 +34828,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>154</v>
+        <v>10.69859549266249</v>
       </c>
       <c r="M3" t="n">
-        <v>143.5960134055608</v>
+        <v>137.0791822851152</v>
       </c>
       <c r="N3" t="n">
         <v>154</v>
@@ -34840,7 +34840,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>4.181764372216961</v>
+        <v>154</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,13 +34877,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>15.9510536994518</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34931,22 +34931,22 @@
         <v>46.01732357583307</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>154</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>142.8742545390233</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -35059,22 +35059,22 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>169</v>
       </c>
-      <c r="K6" t="n">
-        <v>151.4731216790547</v>
-      </c>
       <c r="L6" t="n">
-        <v>10.69859549266249</v>
+        <v>162.1717171717171</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="O6" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>169</v>
@@ -35138,7 +35138,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35171,7 +35171,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>66.08071545128708</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>169</v>
@@ -35183,7 +35183,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>9.615362601824769</v>
       </c>
     </row>
     <row r="8">
@@ -35220,13 +35220,13 @@
         <v>56.05766209661822</v>
       </c>
       <c r="K8" t="n">
-        <v>170</v>
+        <v>136.5362864321608</v>
       </c>
       <c r="L8" t="n">
-        <v>169.3853366834172</v>
+        <v>169.3853366834171</v>
       </c>
       <c r="M8" t="n">
-        <v>13.02151532283553</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>46.48522889067477</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35296,7 +35296,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>170</v>
+        <v>158.9495487590961</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -35305,16 +35305,16 @@
         <v>170</v>
       </c>
       <c r="M9" t="n">
-        <v>163.1313131313131</v>
+        <v>170</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>170</v>
+        <v>4.181764372216961</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35360,10 +35360,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>155.437602568306</v>
@@ -35372,16 +35372,16 @@
         <v>170</v>
       </c>
       <c r="I10" t="n">
-        <v>103.0574713677055</v>
+        <v>132.2411617022572</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>167.4179147234471</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>48.03463413730282</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35457,7 +35457,7 @@
         <v>56.05766209661822</v>
       </c>
       <c r="K11" t="n">
-        <v>136.5362864321608</v>
+        <v>172</v>
       </c>
       <c r="L11" t="n">
         <v>169.3853366834171</v>
@@ -35466,7 +35466,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>18.94070724202746</v>
       </c>
       <c r="O11" t="n">
         <v>110.6023666068121</v>
@@ -35475,7 +35475,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q11" t="n">
-        <v>54.40442080986672</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35539,7 +35539,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>172</v>
+        <v>165.0505050505051</v>
       </c>
       <c r="M12" t="n">
         <v>172</v>
@@ -35551,7 +35551,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>165.050505050505</v>
+        <v>172</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>56.05766209661822</v>
       </c>
       <c r="K14" t="n">
+        <v>136.5362864321608</v>
+      </c>
+      <c r="L14" t="n">
         <v>172</v>
       </c>
-      <c r="L14" t="n">
-        <v>170.3904763470748</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>33.85418991491398</v>
       </c>
       <c r="O14" t="n">
         <v>110.6023666068121</v>
@@ -35773,22 +35773,22 @@
         <v>172</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>154.3519095578426</v>
       </c>
       <c r="L15" t="n">
-        <v>172</v>
+        <v>10.69859549266249</v>
       </c>
       <c r="M15" t="n">
         <v>172</v>
       </c>
       <c r="N15" t="n">
-        <v>160.868740678288</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>4.181764372216961</v>
+        <v>172</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35825,34 +35825,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>63.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>78.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>65.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>70.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>76.61714403225807</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>106.437602568306</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>126.509627996742</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>118.4179147234471</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35879,22 +35879,22 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>143.0326466084964</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.85566997822604</v>
       </c>
       <c r="V16" t="n">
-        <v>16.66588256695586</v>
+        <v>151.8296897837838</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>103.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>63.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -36010,22 +36010,22 @@
         <v>172</v>
       </c>
       <c r="K18" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>10.69859549266249</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="N18" t="n">
+        <v>172</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
         <v>154.3519095578426</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>172</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36062,25 +36062,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>63.88619966292134</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>35.50955136635814</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>65.46378194444452</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>70.01909516304346</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>76.61714403225807</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>126.509627996742</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -36116,13 +36116,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>114.1757103819838</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>151.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>124.6271901612903</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>173.8156182600203</v>
+        <v>56.05766209661822</v>
       </c>
       <c r="K20" t="n">
-        <v>136.5362864321608</v>
+        <v>188</v>
       </c>
       <c r="L20" t="n">
-        <v>169.3853366834171</v>
+        <v>188</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>13.74401170061007</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -36183,7 +36183,7 @@
         <v>110.6023666068121</v>
       </c>
       <c r="P20" t="n">
-        <v>154.0644324216302</v>
+        <v>188</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36247,13 +36247,13 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>188</v>
       </c>
-      <c r="L21" t="n">
-        <v>180.4040404040404</v>
-      </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="N21" t="n">
         <v>188</v>
@@ -36262,7 +36262,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>188</v>
+        <v>180.4040404040404</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36302,7 +36302,7 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>78.27475335195533</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -36317,16 +36317,16 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>126.509627996742</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>31.31388413329777</v>
+        <v>167.6981378136714</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>118.4179147234471</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>143.0326466084964</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -36368,7 +36368,7 @@
         <v>103.5563545698924</v>
       </c>
       <c r="Y22" t="n">
-        <v>63.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -36408,7 +36408,7 @@
         <v>136.5362864321608</v>
       </c>
       <c r="L23" t="n">
-        <v>191.6455317496575</v>
+        <v>268.9787327212152</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36417,13 +36417,13 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>110.6023666068121</v>
+      </c>
+      <c r="P23" t="n">
+        <v>154.0644324216302</v>
+      </c>
+      <c r="Q23" t="n">
         <v>342</v>
-      </c>
-      <c r="P23" t="n">
-        <v>342</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36536,13 +36536,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>63.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>78.27475335195533</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>65.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>70.01909516304346</v>
@@ -36554,7 +36554,7 @@
         <v>106.437602568306</v>
       </c>
       <c r="H25" t="n">
-        <v>13.24336693767719</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>188.8458230684063</v>
@@ -36590,22 +36590,22 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>143.0326466084964</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>96.23984708171544</v>
       </c>
       <c r="V25" t="n">
-        <v>151.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>124.6271901612903</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>103.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>63.53464715053764</v>
       </c>
     </row>
     <row r="26">
@@ -36639,7 +36639,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>56.05766209661822</v>
+        <v>173.8156182600203</v>
       </c>
       <c r="K26" t="n">
         <v>136.5362864321608</v>
@@ -36660,7 +36660,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q26" t="n">
-        <v>117.7579561634021</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,22 +36718,22 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>179.4675401999399</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L27" t="n">
-        <v>180.4040404040404</v>
+        <v>10.69859549266249</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>178.237904711438</v>
       </c>
       <c r="N27" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>188</v>
@@ -36876,7 +36876,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>114.4216788660809</v>
+        <v>56.05766209661822</v>
       </c>
       <c r="K29" t="n">
         <v>136.5362864321608</v>
@@ -36897,7 +36897,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>58.36401676946264</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36958,22 +36958,22 @@
         <v>173</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L30" t="n">
+        <v>10.69859549266249</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>155.3115055174385</v>
+      </c>
+      <c r="P30" t="n">
         <v>173</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>173</v>
-      </c>
-      <c r="O30" t="n">
-        <v>161.8283366378841</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4.181764372216961</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -37013,31 +37013,31 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>79.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>66.46378194444452</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>77.61714403225807</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>127.509627996742</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>160.4915695827166</v>
+        <v>173</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>119.4179147234471</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0.03463413730280251</v>
@@ -37067,16 +37067,16 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>173</v>
+        <v>162.99259738285</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>125.6271901612903</v>
       </c>
       <c r="X31" t="n">
-        <v>104.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -37119,10 +37119,10 @@
         <v>172</v>
       </c>
       <c r="L32" t="n">
-        <v>169.3853366834171</v>
+        <v>170.3904763470748</v>
       </c>
       <c r="M32" t="n">
-        <v>18.94070724202746</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -37131,7 +37131,7 @@
         <v>110.6023666068121</v>
       </c>
       <c r="P32" t="n">
-        <v>154.0644324216302</v>
+        <v>172</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37198,19 +37198,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>165.0505050505051</v>
+        <v>172</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="N33" t="n">
         <v>172</v>
       </c>
       <c r="O33" t="n">
-        <v>172</v>
+        <v>160.868740678288</v>
       </c>
       <c r="P33" t="n">
-        <v>172</v>
+        <v>4.181764372216961</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37265,58 +37265,58 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>65.95950333007501</v>
+      </c>
+      <c r="U34" t="n">
         <v>172</v>
       </c>
-      <c r="I34" t="n">
-        <v>115.5979561897551</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="V34" t="n">
         <v>172</v>
       </c>
-      <c r="K34" t="n">
-        <v>170.4179147234471</v>
-      </c>
-      <c r="L34" t="n">
-        <v>51.03463413730282</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>155.5563545698924</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>115.5346471505376</v>
       </c>
     </row>
     <row r="35">
@@ -37353,13 +37353,13 @@
         <v>56.05766209661822</v>
       </c>
       <c r="K35" t="n">
-        <v>170</v>
+        <v>136.5362864321608</v>
       </c>
       <c r="L35" t="n">
         <v>169.3853366834172</v>
       </c>
       <c r="M35" t="n">
-        <v>13.02151532283553</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>46.48522889067477</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K36" t="n">
         <v>170</v>
@@ -37438,16 +37438,16 @@
         <v>10.69859549266249</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="N36" t="n">
-        <v>152.4327176386506</v>
+        <v>148.2509532664337</v>
       </c>
       <c r="O36" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>170</v>
+        <v>4.181764372216961</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37499,13 +37499,13 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>158.437602568306</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>170</v>
+        <v>128.5576349855876</v>
       </c>
       <c r="I37" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>51.03463413730282</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37538,10 +37538,10 @@
         <v>49.01732357583307</v>
       </c>
       <c r="T37" t="n">
-        <v>74.64175284987118</v>
+        <v>170</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -37550,7 +37550,7 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>155.5563545698924</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>56.05766209661822</v>
+        <v>102.5428909872929</v>
       </c>
       <c r="K38" t="n">
-        <v>170</v>
+        <v>136.5362864321608</v>
       </c>
       <c r="L38" t="n">
-        <v>169.3853366834173</v>
+        <v>169.3853366834172</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -37608,7 +37608,7 @@
         <v>154.0644324216302</v>
       </c>
       <c r="Q38" t="n">
-        <v>13.02151532283547</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,13 +37666,13 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K39" t="n">
         <v>170</v>
       </c>
       <c r="L39" t="n">
-        <v>170</v>
+        <v>163.1313131313131</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -37681,7 +37681,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>163.1313131313131</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>170</v>
@@ -37727,7 +37727,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>7.574958561420631</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -37745,7 +37745,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K40" t="n">
         <v>170</v>
@@ -37772,22 +37772,22 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>49.01732357583307</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>114.11398955548</v>
       </c>
       <c r="V40" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>155.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -37830,7 +37830,7 @@
         <v>170</v>
       </c>
       <c r="L41" t="n">
-        <v>169.3853366834173</v>
+        <v>169.3853366834172</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -37903,10 +37903,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="K42" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>170</v>
@@ -38143,7 +38143,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>147.7777777777777</v>
+        <v>154</v>
       </c>
       <c r="L45" t="n">
         <v>154</v>
@@ -38155,7 +38155,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>154</v>
+        <v>147.7777777777777</v>
       </c>
       <c r="P45" t="n">
         <v>154</v>
